--- a/Tasks.xlsx
+++ b/Tasks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pas02\Nextcloud\Documents\03_Data Science - Uni Stuttgart\06_SoS 2026\04_Software Engineering\Group project 3\ai-travel-planner\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16BF89DB-421B-404A-A737-C34804FD6E69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B71A8C57-1159-469E-9F91-6C2F66974ADF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{834F46D4-8CFA-4605-9F2C-653FA769D6F4}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="204">
   <si>
     <t>Project Setup</t>
   </si>
@@ -729,30 +729,35 @@
     <t># completed on day</t>
   </si>
   <si>
-    <t># tasks left</t>
-  </si>
-  <si>
-    <t>optimal</t>
-  </si>
-  <si>
     <t>real</t>
   </si>
   <si>
     <t>Completed on day</t>
+  </si>
+  <si>
+    <t>ideal</t>
+  </si>
+  <si>
+    <t>Burn-down</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Philipp</t>
+  </si>
+  <si>
+    <t>Pascal</t>
+  </si>
+  <si>
+    <t>Jacopo</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -810,27 +815,26 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -880,7 +884,7 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="de-DE" b="1"/>
-              <a:t>Burn-down chart (day 1)</a:t>
+              <a:t>Alpha Sprint Burn-down chart (day 2)</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -921,15 +925,20 @@
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
-            <c:v>ideal</c:v>
+            <c:strRef>
+              <c:f>Tabelle1!$K$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>ideal</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:tx>
           <c:spPr>
             <a:ln w="28575" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent1">
-                  <a:lumMod val="60000"/>
-                  <a:lumOff val="40000"/>
-                </a:schemeClr>
+                <a:schemeClr val="accent1"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -940,7 +949,7 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Tabelle1!$G$5:$G$10</c:f>
+              <c:f>Tabelle1!$H$5:$H$10</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
@@ -967,7 +976,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Tabelle1!$J$5:$J$10</c:f>
+              <c:f>Tabelle1!$K$5:$K$10</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
@@ -1003,7 +1012,15 @@
           <c:idx val="1"/>
           <c:order val="1"/>
           <c:tx>
-            <c:v>real</c:v>
+            <c:strRef>
+              <c:f>Tabelle1!$L$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>real</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:tx>
           <c:spPr>
             <a:ln w="28575" cap="rnd">
@@ -1019,7 +1036,7 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Tabelle1!$G$5:$G$10</c:f>
+              <c:f>Tabelle1!$H$5:$H$10</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
@@ -1046,14 +1063,17 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Tabelle1!$L$5:$L$6</c:f>
+              <c:f>Tabelle1!$L$5:$L$7</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>165</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>137</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>137</c:v>
                 </c:pt>
               </c:numCache>
@@ -1919,13 +1939,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
+      <xdr:col>6</xdr:col>
       <xdr:colOff>723900</xdr:colOff>
       <xdr:row>12</xdr:row>
       <xdr:rowOff>14287</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
+      <xdr:col>14</xdr:col>
       <xdr:colOff>676275</xdr:colOff>
       <xdr:row>28</xdr:row>
       <xdr:rowOff>161925</xdr:rowOff>
@@ -2273,2110 +2293,2300 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67F1D602-D536-4BC9-865A-CD2C06CAE9C2}">
-  <dimension ref="B2:L193"/>
+  <dimension ref="B2:M193"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="11.42578125" style="2"/>
-    <col min="2" max="2" width="6.85546875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="29.7109375" style="2" customWidth="1"/>
-    <col min="4" max="4" width="66.140625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="12.5703125" style="2" customWidth="1"/>
-    <col min="6" max="16384" width="11.42578125" style="2"/>
+    <col min="2" max="2" width="6.85546875" customWidth="1"/>
+    <col min="3" max="3" width="22.85546875" customWidth="1"/>
+    <col min="4" max="4" width="29.7109375" customWidth="1"/>
+    <col min="5" max="5" width="66.140625" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" ht="21">
-      <c r="B2" s="6" t="s">
+    <row r="2" spans="2:13" ht="21">
+      <c r="B2" s="5" t="s">
         <v>191</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="C2" s="5"/>
+      <c r="H2" s="5" t="s">
         <v>192</v>
       </c>
-      <c r="K2" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="2:12">
-      <c r="D3" s="5"/>
-      <c r="J3" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="4" spans="2:12">
+    </row>
+    <row r="3" spans="2:13">
+      <c r="E3" s="4"/>
+      <c r="K3" t="s">
+        <v>199</v>
+      </c>
+      <c r="L3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="2:13">
       <c r="B4" s="1" t="s">
         <v>188</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="G4" s="1" t="s">
+      <c r="F4" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="J4" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="K4" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="L4" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="K4" s="1" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="5" spans="2:12">
-      <c r="B5" s="2">
-        <v>1</v>
-      </c>
-      <c r="C5" s="4" t="s">
+    </row>
+    <row r="5" spans="2:13">
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5" t="s">
+        <v>201</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E5" s="2">
-        <v>1</v>
-      </c>
-      <c r="G5" s="2">
+      <c r="E5" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="H5">
         <v>0</v>
       </c>
-      <c r="H5" s="2">
+      <c r="I5">
         <v>0</v>
       </c>
-      <c r="I5" s="2">
-        <f>COUNTIF($E$5:$E$192,G5)</f>
+      <c r="J5">
+        <f>COUNTIF($F$5:$F$192,H5)</f>
         <v>0</v>
       </c>
-      <c r="J5" s="2">
+      <c r="K5">
         <v>165</v>
       </c>
-      <c r="K5" s="2">
+      <c r="L5">
         <v>165</v>
       </c>
-      <c r="L5" s="2">
-        <f>IF(G5&gt;$K$2,"",K5)</f>
-        <v>165</v>
-      </c>
-    </row>
-    <row r="6" spans="2:12">
-      <c r="B6" s="2">
-        <v>1</v>
-      </c>
-      <c r="C6" s="4" t="s">
+    </row>
+    <row r="6" spans="2:13">
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6" t="s">
+        <v>201</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="E6" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="2">
-        <v>1</v>
-      </c>
-      <c r="G6" s="2">
-        <v>1</v>
-      </c>
-      <c r="H6" s="2">
-        <f>COUNTIF($B$5:$B$1900,G6)</f>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <f>COUNTIF($B$5:$B$1900,H6)</f>
         <v>33</v>
       </c>
-      <c r="I6" s="2">
-        <f t="shared" ref="I6:I10" si="0">COUNTIF($E$5:$E$192,G6)</f>
+      <c r="J6">
+        <f t="shared" ref="J6:J10" si="0">COUNTIF($F$5:$F$192,H6)</f>
         <v>28</v>
       </c>
-      <c r="J6" s="2">
-        <f>J5-H6</f>
+      <c r="K6">
+        <f>K5-I6</f>
         <v>132</v>
       </c>
-      <c r="K6" s="2">
-        <f>K5-I6</f>
+      <c r="L6">
+        <f>IF(H6&gt;$L$3,"",L5-J6)</f>
         <v>137</v>
       </c>
-      <c r="L6" s="2">
-        <f t="shared" ref="L6:L10" si="1">IF(G6&gt;$K$2,"",K6)</f>
-        <v>137</v>
-      </c>
-    </row>
-    <row r="7" spans="2:12">
-      <c r="B7" s="2">
-        <v>1</v>
-      </c>
-      <c r="C7" s="4" t="s">
+    </row>
+    <row r="7" spans="2:13">
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7" t="s">
+        <v>201</v>
+      </c>
+      <c r="D7" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="E7" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="E7" s="2">
-        <v>1</v>
-      </c>
-      <c r="G7" s="2">
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="H7">
         <v>2</v>
       </c>
-      <c r="H7" s="2">
-        <f t="shared" ref="H7:H10" si="2">COUNTIF($B$5:$B$1900,G7)</f>
+      <c r="I7">
+        <f t="shared" ref="I7:I10" si="1">COUNTIF($B$5:$B$1900,H7)</f>
         <v>33</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J7" s="2">
-        <f t="shared" ref="J7:J10" si="3">J6-H7</f>
+      <c r="K7">
+        <f t="shared" ref="K7:K10" si="2">K6-I7</f>
         <v>99</v>
       </c>
-      <c r="K7" s="2">
-        <f t="shared" ref="K7:K10" si="4">K6-I7</f>
+      <c r="L7">
+        <f t="shared" ref="L7:L10" si="3">IF(H7&gt;$L$3,"",L6-J7)</f>
         <v>137</v>
       </c>
-      <c r="L7" s="2" t="str">
+      <c r="M7">
+        <f>IF(H7&gt;$L$3,"",L7)</f>
+        <v>137</v>
+      </c>
+    </row>
+    <row r="8" spans="2:13">
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8" t="s">
+        <v>201</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="H8">
+        <v>3</v>
+      </c>
+      <c r="I8">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="8" spans="2:12">
-      <c r="B8" s="2">
-        <v>1</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E8" s="2">
-        <v>1</v>
-      </c>
-      <c r="G8" s="2">
-        <v>3</v>
-      </c>
-      <c r="H8" s="2">
-        <f t="shared" si="2"/>
         <v>33</v>
       </c>
-      <c r="I8" s="2">
+      <c r="J8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J8" s="2">
+      <c r="K8">
+        <f t="shared" si="2"/>
+        <v>66</v>
+      </c>
+      <c r="L8" t="str">
         <f t="shared" si="3"/>
-        <v>66</v>
-      </c>
-      <c r="K8" s="2">
-        <f t="shared" si="4"/>
-        <v>137</v>
-      </c>
-      <c r="L8" s="2" t="str">
+        <v/>
+      </c>
+      <c r="M8" t="str">
+        <f>IF(H8&gt;$L$3,"",L8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" spans="2:13">
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9" t="s">
+        <v>201</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="H9">
+        <v>4</v>
+      </c>
+      <c r="I9">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="9" spans="2:12">
-      <c r="B9" s="2">
-        <v>1</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E9" s="2">
-        <v>1</v>
-      </c>
-      <c r="G9" s="2">
-        <v>4</v>
-      </c>
-      <c r="H9" s="2">
-        <f t="shared" si="2"/>
         <v>38</v>
       </c>
-      <c r="I9" s="2">
+      <c r="J9">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J9" s="2">
-        <f t="shared" si="3"/>
-        <v>28</v>
-      </c>
-      <c r="K9" s="2">
-        <f t="shared" si="4"/>
-        <v>137</v>
-      </c>
-      <c r="L9" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="10" spans="2:12">
-      <c r="B10" s="2">
-        <v>1</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E10" s="2">
-        <v>1</v>
-      </c>
-      <c r="G10" s="2">
-        <v>5</v>
-      </c>
-      <c r="H10" s="2">
+      <c r="K9">
         <f t="shared" si="2"/>
         <v>28</v>
       </c>
-      <c r="I10" s="2">
+      <c r="L9" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M9" t="str">
+        <f>IF(H9&gt;$L$3,"",L9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" spans="2:13">
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10" t="s">
+        <v>201</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="H10">
+        <v>5</v>
+      </c>
+      <c r="I10">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+      <c r="J10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J10" s="2">
+      <c r="K10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L10" t="str">
         <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M10" t="str">
+        <f>IF(H10&gt;$L$3,"",L10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" spans="2:13">
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11" t="s">
+        <v>201</v>
+      </c>
+      <c r="D11" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="K10" s="2">
-        <f t="shared" si="4"/>
+      <c r="E11" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="I11" s="8">
+        <f>SUM(I6:I10)</f>
+        <v>165</v>
+      </c>
+    </row>
+    <row r="12" spans="2:13">
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12" t="s">
+        <v>201</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="2:13">
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14" t="s">
+        <v>202</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="2:13">
+      <c r="B15">
+        <v>1</v>
+      </c>
+      <c r="C15" t="s">
+        <v>202</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="2:13">
+      <c r="B16">
+        <v>1</v>
+      </c>
+      <c r="C16" t="s">
+        <v>202</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6">
+      <c r="B17">
+        <v>1</v>
+      </c>
+      <c r="C17" t="s">
+        <v>202</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6">
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18" t="s">
+        <v>202</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="2:6">
+      <c r="B19">
+        <v>1</v>
+      </c>
+      <c r="C19" t="s">
+        <v>202</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6">
+      <c r="B20">
+        <v>1</v>
+      </c>
+      <c r="C20" t="s">
+        <v>202</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="2:6">
+      <c r="B22">
+        <v>1</v>
+      </c>
+      <c r="C22" t="s">
+        <v>203</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="2:6">
+      <c r="B23">
+        <v>1</v>
+      </c>
+      <c r="C23" t="s">
+        <v>203</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="2:6">
+      <c r="B24">
+        <v>1</v>
+      </c>
+      <c r="C24" t="s">
+        <v>203</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="2:6">
+      <c r="B25">
+        <v>1</v>
+      </c>
+      <c r="C25" t="s">
+        <v>203</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="2:6">
+      <c r="B26">
+        <v>1</v>
+      </c>
+      <c r="C26" t="s">
+        <v>203</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6">
+      <c r="B27">
+        <v>1</v>
+      </c>
+      <c r="C27" t="s">
+        <v>203</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="2:6">
+      <c r="B28">
+        <v>1</v>
+      </c>
+      <c r="C28" t="s">
+        <v>203</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="2:6">
+      <c r="B29">
+        <v>1</v>
+      </c>
+      <c r="C29" t="s">
+        <v>203</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6">
+      <c r="B30">
+        <v>1</v>
+      </c>
+      <c r="C30" t="s">
+        <v>203</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="2:6">
+      <c r="B31">
+        <v>1</v>
+      </c>
+      <c r="C31" t="s">
+        <v>203</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="2:6">
+      <c r="B32">
+        <v>1</v>
+      </c>
+      <c r="C32" t="s">
+        <v>203</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="2:6">
+      <c r="B33">
+        <v>1</v>
+      </c>
+      <c r="C33" t="s">
+        <v>203</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="2:6">
+      <c r="B34">
+        <v>1</v>
+      </c>
+      <c r="C34" t="s">
+        <v>203</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="2:6">
+      <c r="B36">
+        <v>1</v>
+      </c>
+      <c r="C36" t="s">
+        <v>203</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="37" spans="2:6">
+      <c r="B37">
+        <v>1</v>
+      </c>
+      <c r="C37" t="s">
+        <v>203</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="38" spans="2:6">
+      <c r="B38">
+        <v>1</v>
+      </c>
+      <c r="C38" t="s">
+        <v>203</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="39" spans="2:6">
+      <c r="B39">
+        <v>1</v>
+      </c>
+      <c r="C39" t="s">
+        <v>203</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="40" spans="2:6">
+      <c r="B40">
+        <v>1</v>
+      </c>
+      <c r="C40" t="s">
+        <v>203</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="42" spans="2:6">
+      <c r="B42">
+        <v>2</v>
+      </c>
+      <c r="C42" t="s">
+        <v>201</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="43" spans="2:6">
+      <c r="B43">
+        <v>2</v>
+      </c>
+      <c r="C43" t="s">
+        <v>201</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="44" spans="2:6">
+      <c r="B44">
+        <v>2</v>
+      </c>
+      <c r="C44" t="s">
+        <v>201</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="45" spans="2:6">
+      <c r="B45">
+        <v>2</v>
+      </c>
+      <c r="C45" t="s">
+        <v>201</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="46" spans="2:6">
+      <c r="B46">
+        <v>2</v>
+      </c>
+      <c r="C46" t="s">
+        <v>201</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="47" spans="2:6">
+      <c r="B47">
+        <v>2</v>
+      </c>
+      <c r="C47" t="s">
+        <v>201</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="48" spans="2:6">
+      <c r="B48">
+        <v>2</v>
+      </c>
+      <c r="C48" t="s">
+        <v>201</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="50" spans="2:5">
+      <c r="B50">
+        <v>2</v>
+      </c>
+      <c r="C50" t="s">
+        <v>201</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="51" spans="2:5">
+      <c r="B51">
+        <v>2</v>
+      </c>
+      <c r="C51" t="s">
+        <v>201</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="52" spans="2:5">
+      <c r="B52">
+        <v>2</v>
+      </c>
+      <c r="C52" t="s">
+        <v>201</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="53" spans="2:5">
+      <c r="B53">
+        <v>2</v>
+      </c>
+      <c r="C53" t="s">
+        <v>201</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="54" spans="2:5">
+      <c r="B54">
+        <v>2</v>
+      </c>
+      <c r="C54" t="s">
+        <v>201</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="55" spans="2:5">
+      <c r="B55">
+        <v>2</v>
+      </c>
+      <c r="C55" t="s">
+        <v>201</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="57" spans="2:5">
+      <c r="B57">
+        <v>2</v>
+      </c>
+      <c r="C57" t="s">
+        <v>202</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="58" spans="2:5">
+      <c r="B58">
+        <v>2</v>
+      </c>
+      <c r="C58" t="s">
+        <v>202</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="59" spans="2:5">
+      <c r="B59">
+        <v>2</v>
+      </c>
+      <c r="C59" t="s">
+        <v>202</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="60" spans="2:5">
+      <c r="B60">
+        <v>2</v>
+      </c>
+      <c r="C60" t="s">
+        <v>202</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="61" spans="2:5">
+      <c r="B61">
+        <v>2</v>
+      </c>
+      <c r="C61" t="s">
+        <v>202</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="62" spans="2:5">
+      <c r="B62">
+        <v>2</v>
+      </c>
+      <c r="C62" t="s">
+        <v>202</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="64" spans="2:5">
+      <c r="B64">
+        <v>2</v>
+      </c>
+      <c r="C64" t="s">
+        <v>202</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="65" spans="2:5">
+      <c r="B65">
+        <v>2</v>
+      </c>
+      <c r="C65" t="s">
+        <v>202</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="66" spans="2:5">
+      <c r="B66">
+        <v>2</v>
+      </c>
+      <c r="C66" t="s">
+        <v>202</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="67" spans="2:5">
+      <c r="B67">
+        <v>2</v>
+      </c>
+      <c r="C67" t="s">
+        <v>202</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="68" spans="2:5">
+      <c r="B68">
+        <v>2</v>
+      </c>
+      <c r="C68" t="s">
+        <v>202</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="69" spans="2:5">
+      <c r="B69">
+        <v>2</v>
+      </c>
+      <c r="C69" t="s">
+        <v>202</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="71" spans="2:5">
+      <c r="B71">
+        <v>2</v>
+      </c>
+      <c r="C71" t="s">
+        <v>203</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="72" spans="2:5">
+      <c r="B72">
+        <v>2</v>
+      </c>
+      <c r="C72" t="s">
+        <v>203</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="73" spans="2:5">
+      <c r="B73">
+        <v>2</v>
+      </c>
+      <c r="C73" t="s">
+        <v>203</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="74" spans="2:5">
+      <c r="B74">
+        <v>2</v>
+      </c>
+      <c r="C74" t="s">
+        <v>203</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="75" spans="2:5">
+      <c r="B75">
+        <v>2</v>
+      </c>
+      <c r="C75" t="s">
+        <v>203</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="76" spans="2:5">
+      <c r="B76">
+        <v>2</v>
+      </c>
+      <c r="C76" t="s">
+        <v>203</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="77" spans="2:5">
+      <c r="B77">
+        <v>2</v>
+      </c>
+      <c r="C77" t="s">
+        <v>203</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="78" spans="2:5">
+      <c r="B78">
+        <v>2</v>
+      </c>
+      <c r="C78" t="s">
+        <v>203</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="80" spans="2:5">
+      <c r="B80">
+        <v>3</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="81" spans="2:5">
+      <c r="B81">
+        <v>3</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="82" spans="2:5">
+      <c r="B82">
+        <v>3</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="83" spans="2:5">
+      <c r="B83">
+        <v>3</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="85" spans="2:5">
+      <c r="B85">
+        <v>3</v>
+      </c>
+      <c r="D85" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="86" spans="2:5">
+      <c r="B86">
+        <v>3</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="87" spans="2:5">
+      <c r="B87">
+        <v>3</v>
+      </c>
+      <c r="D87" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="88" spans="2:5">
+      <c r="B88">
+        <v>3</v>
+      </c>
+      <c r="D88" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="89" spans="2:5">
+      <c r="B89">
+        <v>3</v>
+      </c>
+      <c r="D89" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="90" spans="2:5">
+      <c r="B90">
+        <v>3</v>
+      </c>
+      <c r="D90" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="91" spans="2:5">
+      <c r="B91">
+        <v>3</v>
+      </c>
+      <c r="D91" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="92" spans="2:5">
+      <c r="B92">
+        <v>3</v>
+      </c>
+      <c r="D92" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="93" spans="2:5">
+      <c r="B93">
+        <v>3</v>
+      </c>
+      <c r="D93" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E93" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="94" spans="2:5">
+      <c r="B94">
+        <v>3</v>
+      </c>
+      <c r="D94" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="95" spans="2:5">
+      <c r="B95">
+        <v>3</v>
+      </c>
+      <c r="D95" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E95" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="97" spans="2:5">
+      <c r="B97">
+        <v>3</v>
+      </c>
+      <c r="D97" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="E97" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="98" spans="2:5">
+      <c r="B98">
+        <v>3</v>
+      </c>
+      <c r="D98" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="E98" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="99" spans="2:5">
+      <c r="B99">
+        <v>3</v>
+      </c>
+      <c r="D99" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="E99" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="100" spans="2:5">
+      <c r="B100">
+        <v>3</v>
+      </c>
+      <c r="D100" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="E100" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="101" spans="2:5">
+      <c r="B101">
+        <v>3</v>
+      </c>
+      <c r="D101" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="E101" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="102" spans="2:5">
+      <c r="B102">
+        <v>3</v>
+      </c>
+      <c r="D102" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="E102" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="103" spans="2:5">
+      <c r="B103">
+        <v>3</v>
+      </c>
+      <c r="D103" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="E103" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="104" spans="2:5">
+      <c r="B104">
+        <v>3</v>
+      </c>
+      <c r="D104" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="E104" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="105" spans="2:5">
+      <c r="B105">
+        <v>3</v>
+      </c>
+      <c r="D105" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="E105" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="106" spans="2:5">
+      <c r="B106">
+        <v>3</v>
+      </c>
+      <c r="D106" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="E106" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="108" spans="2:5">
+      <c r="B108">
+        <v>3</v>
+      </c>
+      <c r="D108" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="E108" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="109" spans="2:5">
+      <c r="B109">
+        <v>3</v>
+      </c>
+      <c r="D109" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="E109" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="110" spans="2:5">
+      <c r="B110">
+        <v>3</v>
+      </c>
+      <c r="D110" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="E110" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="111" spans="2:5">
+      <c r="B111">
+        <v>3</v>
+      </c>
+      <c r="D111" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="E111" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="112" spans="2:5">
+      <c r="B112">
+        <v>3</v>
+      </c>
+      <c r="D112" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="E112" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="114" spans="2:5">
+      <c r="B114">
+        <v>3</v>
+      </c>
+      <c r="D114" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="E114" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="115" spans="2:5">
+      <c r="B115">
+        <v>3</v>
+      </c>
+      <c r="D115" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="E115" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="116" spans="2:5">
+      <c r="B116">
+        <v>3</v>
+      </c>
+      <c r="D116" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="E116" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="118" spans="2:5">
+      <c r="B118">
+        <v>4</v>
+      </c>
+      <c r="D118" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="E118" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="119" spans="2:5">
+      <c r="B119">
+        <v>4</v>
+      </c>
+      <c r="D119" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="E119" s="2" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="120" spans="2:5">
+      <c r="B120">
+        <v>4</v>
+      </c>
+      <c r="D120" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="E120" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="121" spans="2:5">
+      <c r="B121">
+        <v>4</v>
+      </c>
+      <c r="D121" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="E121" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="122" spans="2:5">
+      <c r="B122">
+        <v>4</v>
+      </c>
+      <c r="D122" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="E122" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="123" spans="2:5">
+      <c r="B123">
+        <v>4</v>
+      </c>
+      <c r="D123" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="E123" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="125" spans="2:5">
+      <c r="B125">
+        <v>4</v>
+      </c>
+      <c r="D125" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="E125" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="126" spans="2:5">
+      <c r="B126">
+        <v>4</v>
+      </c>
+      <c r="D126" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="E126" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="127" spans="2:5">
+      <c r="B127">
+        <v>4</v>
+      </c>
+      <c r="D127" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="E127" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="128" spans="2:5">
+      <c r="B128">
+        <v>4</v>
+      </c>
+      <c r="D128" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="E128" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="129" spans="2:5">
+      <c r="B129">
+        <v>4</v>
+      </c>
+      <c r="D129" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="E129" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="130" spans="2:5">
+      <c r="B130">
+        <v>4</v>
+      </c>
+      <c r="D130" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="E130" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="131" spans="2:5">
+      <c r="B131">
+        <v>4</v>
+      </c>
+      <c r="D131" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="E131" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="132" spans="2:5">
+      <c r="B132">
+        <v>4</v>
+      </c>
+      <c r="D132" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="E132" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="133" spans="2:5">
+      <c r="B133">
+        <v>4</v>
+      </c>
+      <c r="D133" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="E133" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="134" spans="2:5">
+      <c r="B134">
+        <v>4</v>
+      </c>
+      <c r="D134" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="E134" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="135" spans="2:5">
+      <c r="B135">
+        <v>4</v>
+      </c>
+      <c r="D135" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="E135" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="137" spans="2:5">
+      <c r="B137">
+        <v>4</v>
+      </c>
+      <c r="D137" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E137" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="138" spans="2:5">
+      <c r="B138">
+        <v>4</v>
+      </c>
+      <c r="D138" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E138" s="2" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="139" spans="2:5">
+      <c r="B139">
+        <v>4</v>
+      </c>
+      <c r="D139" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E139" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="140" spans="2:5">
+      <c r="B140">
+        <v>4</v>
+      </c>
+      <c r="D140" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E140" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="142" spans="2:5">
+      <c r="B142">
+        <v>4</v>
+      </c>
+      <c r="D142" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="E142" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="143" spans="2:5">
+      <c r="B143">
+        <v>4</v>
+      </c>
+      <c r="D143" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="E143" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="144" spans="2:5">
+      <c r="B144">
+        <v>4</v>
+      </c>
+      <c r="D144" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="E144" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="145" spans="2:5">
+      <c r="B145">
+        <v>4</v>
+      </c>
+      <c r="D145" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="E145" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="146" spans="2:5">
+      <c r="B146">
+        <v>4</v>
+      </c>
+      <c r="D146" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="E146" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="147" spans="2:5">
+      <c r="B147">
+        <v>4</v>
+      </c>
+      <c r="D147" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="E147" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="L10" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="11" spans="2:12">
-      <c r="B11" s="2">
-        <v>1</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E11" s="2">
-        <v>1</v>
-      </c>
-      <c r="G11" s="9" t="s">
-        <v>194</v>
-      </c>
-      <c r="H11" s="9">
-        <f>SUM(H6:H10)</f>
+    </row>
+    <row r="148" spans="2:5">
+      <c r="B148">
+        <v>4</v>
+      </c>
+      <c r="D148" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="E148" s="2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="150" spans="2:5">
+      <c r="B150">
+        <v>4</v>
+      </c>
+      <c r="D150" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="E150" s="2" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="151" spans="2:5">
+      <c r="B151">
+        <v>4</v>
+      </c>
+      <c r="D151" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="E151" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="152" spans="2:5">
+      <c r="B152">
+        <v>4</v>
+      </c>
+      <c r="D152" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="E152" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="153" spans="2:5">
+      <c r="B153">
+        <v>4</v>
+      </c>
+      <c r="D153" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="E153" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="154" spans="2:5">
+      <c r="B154">
+        <v>4</v>
+      </c>
+      <c r="D154" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="E154" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="155" spans="2:5">
+      <c r="B155">
+        <v>4</v>
+      </c>
+      <c r="D155" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="E155" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="156" spans="2:5">
+      <c r="B156">
+        <v>4</v>
+      </c>
+      <c r="D156" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="E156" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="157" spans="2:5">
+      <c r="B157">
+        <v>4</v>
+      </c>
+      <c r="D157" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="E157" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="158" spans="2:5">
+      <c r="B158">
+        <v>4</v>
+      </c>
+      <c r="D158" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="E158" s="2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="159" spans="2:5">
+      <c r="B159">
+        <v>4</v>
+      </c>
+      <c r="D159" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="E159" s="2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="161" spans="2:5">
+      <c r="B161">
+        <v>5</v>
+      </c>
+      <c r="D161" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="E161" s="2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="162" spans="2:5">
+      <c r="B162">
+        <v>5</v>
+      </c>
+      <c r="D162" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="E162" s="2" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="163" spans="2:5">
+      <c r="B163">
+        <v>5</v>
+      </c>
+      <c r="D163" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="E163" s="2" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="164" spans="2:5">
+      <c r="B164">
+        <v>5</v>
+      </c>
+      <c r="D164" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="E164" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="165" spans="2:5">
+      <c r="B165">
+        <v>5</v>
+      </c>
+      <c r="D165" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="E165" s="2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="166" spans="2:5">
+      <c r="B166">
+        <v>5</v>
+      </c>
+      <c r="D166" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="E166" s="2" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="167" spans="2:5">
+      <c r="B167">
+        <v>5</v>
+      </c>
+      <c r="D167" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="E167" s="2" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="169" spans="2:5">
+      <c r="B169">
+        <v>5</v>
+      </c>
+      <c r="D169" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="E169" s="2" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="170" spans="2:5">
+      <c r="B170">
+        <v>5</v>
+      </c>
+      <c r="D170" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="E170" s="2" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="171" spans="2:5">
+      <c r="B171">
+        <v>5</v>
+      </c>
+      <c r="D171" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="E171" s="2" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="172" spans="2:5">
+      <c r="B172">
+        <v>5</v>
+      </c>
+      <c r="D172" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="E172" s="2" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="173" spans="2:5">
+      <c r="B173">
+        <v>5</v>
+      </c>
+      <c r="D173" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="E173" s="2" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="175" spans="2:5">
+      <c r="B175">
+        <v>5</v>
+      </c>
+      <c r="D175" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="E175" s="2" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="12" spans="2:12">
-      <c r="B12" s="2">
-        <v>1</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E12" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="2:12">
-      <c r="B14" s="2">
-        <v>1</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E14" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="2:12">
-      <c r="B15" s="2">
-        <v>1</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E15" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="2:12">
-      <c r="B16" s="2">
-        <v>1</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="E16" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="2:5">
-      <c r="B17" s="2">
-        <v>1</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="E17" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="2:5">
-      <c r="B18" s="2">
-        <v>1</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E18" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="2:5">
-      <c r="B19" s="2">
-        <v>1</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E19" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="2:5">
-      <c r="B20" s="2">
-        <v>1</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E20" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="2:5">
-      <c r="B22" s="2">
-        <v>1</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E22" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="2:5">
-      <c r="B23" s="2">
-        <v>1</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E23" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="2:5">
-      <c r="B24" s="2">
-        <v>1</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E24" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="2:5">
-      <c r="B25" s="2">
-        <v>1</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E25" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="2:5">
-      <c r="B26" s="2">
-        <v>1</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E26" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="2:5">
-      <c r="B27" s="2">
-        <v>1</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="2:5">
-      <c r="B28" s="2">
-        <v>1</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E28" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="2:5">
-      <c r="B29" s="2">
-        <v>1</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E29" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="2:5">
-      <c r="B30" s="2">
-        <v>1</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E30" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="2:5">
-      <c r="B31" s="2">
-        <v>1</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E31" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="2:5">
-      <c r="B32" s="2">
-        <v>1</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E32" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="2:5">
-      <c r="B33" s="2">
-        <v>1</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E33" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="2:5">
-      <c r="B34" s="2">
-        <v>1</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E34" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="2:5">
-      <c r="B36" s="2">
-        <v>1</v>
-      </c>
-      <c r="C36" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="37" spans="2:5">
-      <c r="B37" s="2">
-        <v>1</v>
-      </c>
-      <c r="C37" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="38" spans="2:5">
-      <c r="B38" s="2">
-        <v>1</v>
-      </c>
-      <c r="C38" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="39" spans="2:5">
-      <c r="B39" s="2">
-        <v>1</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="40" spans="2:5">
-      <c r="B40" s="2">
-        <v>1</v>
-      </c>
-      <c r="C40" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="42" spans="2:5">
-      <c r="B42" s="2">
-        <v>2</v>
-      </c>
-      <c r="C42" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="43" spans="2:5">
-      <c r="B43" s="2">
-        <v>2</v>
-      </c>
-      <c r="C43" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="44" spans="2:5">
-      <c r="B44" s="2">
-        <v>2</v>
-      </c>
-      <c r="C44" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="45" spans="2:5">
-      <c r="B45" s="2">
-        <v>2</v>
-      </c>
-      <c r="C45" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="46" spans="2:5">
-      <c r="B46" s="2">
-        <v>2</v>
-      </c>
-      <c r="C46" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="47" spans="2:5">
-      <c r="B47" s="2">
-        <v>2</v>
-      </c>
-      <c r="C47" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="48" spans="2:5">
-      <c r="B48" s="2">
-        <v>2</v>
-      </c>
-      <c r="C48" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="50" spans="2:4">
-      <c r="B50" s="2">
-        <v>2</v>
-      </c>
-      <c r="C50" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="51" spans="2:4">
-      <c r="B51" s="2">
-        <v>2</v>
-      </c>
-      <c r="C51" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="52" spans="2:4">
-      <c r="B52" s="2">
-        <v>2</v>
-      </c>
-      <c r="C52" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D52" s="3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="53" spans="2:4">
-      <c r="B53" s="2">
-        <v>2</v>
-      </c>
-      <c r="C53" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D53" s="3" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="54" spans="2:4">
-      <c r="B54" s="2">
-        <v>2</v>
-      </c>
-      <c r="C54" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D54" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="55" spans="2:4">
-      <c r="B55" s="2">
-        <v>2</v>
-      </c>
-      <c r="C55" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D55" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="57" spans="2:4">
-      <c r="B57" s="2">
-        <v>2</v>
-      </c>
-      <c r="C57" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="D57" s="3" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="58" spans="2:4">
-      <c r="B58" s="2">
-        <v>2</v>
-      </c>
-      <c r="C58" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="D58" s="3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="59" spans="2:4">
-      <c r="B59" s="2">
-        <v>2</v>
-      </c>
-      <c r="C59" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="D59" s="3" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="60" spans="2:4">
-      <c r="B60" s="2">
-        <v>2</v>
-      </c>
-      <c r="C60" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="D60" s="3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="61" spans="2:4">
-      <c r="B61" s="2">
-        <v>2</v>
-      </c>
-      <c r="C61" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="D61" s="3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="62" spans="2:4">
-      <c r="B62" s="2">
-        <v>2</v>
-      </c>
-      <c r="C62" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="D62" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="64" spans="2:4">
-      <c r="B64" s="2">
-        <v>2</v>
-      </c>
-      <c r="C64" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D64" s="3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="65" spans="2:4">
-      <c r="B65" s="2">
-        <v>2</v>
-      </c>
-      <c r="C65" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D65" s="3" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="66" spans="2:4">
-      <c r="B66" s="2">
-        <v>2</v>
-      </c>
-      <c r="C66" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D66" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="67" spans="2:4">
-      <c r="B67" s="2">
-        <v>2</v>
-      </c>
-      <c r="C67" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D67" s="3" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="68" spans="2:4">
-      <c r="B68" s="2">
-        <v>2</v>
-      </c>
-      <c r="C68" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D68" s="3" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="69" spans="2:4">
-      <c r="B69" s="2">
-        <v>2</v>
-      </c>
-      <c r="C69" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D69" s="3" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="71" spans="2:4">
-      <c r="B71" s="2">
-        <v>2</v>
-      </c>
-      <c r="C71" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="D71" s="3" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="72" spans="2:4">
-      <c r="B72" s="2">
-        <v>2</v>
-      </c>
-      <c r="C72" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="D72" s="3" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="73" spans="2:4">
-      <c r="B73" s="2">
-        <v>2</v>
-      </c>
-      <c r="C73" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="D73" s="3" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="74" spans="2:4">
-      <c r="B74" s="2">
-        <v>2</v>
-      </c>
-      <c r="C74" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="D74" s="3" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="75" spans="2:4">
-      <c r="B75" s="2">
-        <v>2</v>
-      </c>
-      <c r="C75" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="D75" s="3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="76" spans="2:4">
-      <c r="B76" s="2">
-        <v>2</v>
-      </c>
-      <c r="C76" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="D76" s="3" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="77" spans="2:4">
-      <c r="B77" s="2">
-        <v>2</v>
-      </c>
-      <c r="C77" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="D77" s="3" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="78" spans="2:4">
-      <c r="B78" s="2">
-        <v>2</v>
-      </c>
-      <c r="C78" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="D78" s="3" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="80" spans="2:4">
-      <c r="B80" s="2">
-        <v>3</v>
-      </c>
-      <c r="C80" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="D80" s="3" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="81" spans="2:4">
-      <c r="B81" s="2">
-        <v>3</v>
-      </c>
-      <c r="C81" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="D81" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="82" spans="2:4">
-      <c r="B82" s="2">
-        <v>3</v>
-      </c>
-      <c r="C82" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="D82" s="3" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="83" spans="2:4">
-      <c r="B83" s="2">
-        <v>3</v>
-      </c>
-      <c r="C83" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="D83" s="3" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="85" spans="2:4">
-      <c r="B85" s="2">
-        <v>3</v>
-      </c>
-      <c r="C85" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="D85" s="3" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="86" spans="2:4">
-      <c r="B86" s="2">
-        <v>3</v>
-      </c>
-      <c r="C86" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="D86" s="3" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="87" spans="2:4">
-      <c r="B87" s="2">
-        <v>3</v>
-      </c>
-      <c r="C87" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="D87" s="3" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="88" spans="2:4">
-      <c r="B88" s="2">
-        <v>3</v>
-      </c>
-      <c r="C88" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="D88" s="3" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="89" spans="2:4">
-      <c r="B89" s="2">
-        <v>3</v>
-      </c>
-      <c r="C89" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="D89" s="3" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="90" spans="2:4">
-      <c r="B90" s="2">
-        <v>3</v>
-      </c>
-      <c r="C90" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="D90" s="3" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="91" spans="2:4">
-      <c r="B91" s="2">
-        <v>3</v>
-      </c>
-      <c r="C91" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="D91" s="3" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="92" spans="2:4">
-      <c r="B92" s="2">
-        <v>3</v>
-      </c>
-      <c r="C92" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="D92" s="3" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="93" spans="2:4">
-      <c r="B93" s="2">
-        <v>3</v>
-      </c>
-      <c r="C93" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="D93" s="3" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="94" spans="2:4">
-      <c r="B94" s="2">
-        <v>3</v>
-      </c>
-      <c r="C94" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="D94" s="3" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="95" spans="2:4">
-      <c r="B95" s="2">
-        <v>3</v>
-      </c>
-      <c r="C95" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="D95" s="3" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="97" spans="2:4">
-      <c r="B97" s="2">
-        <v>3</v>
-      </c>
-      <c r="C97" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="D97" s="3" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="98" spans="2:4">
-      <c r="B98" s="2">
-        <v>3</v>
-      </c>
-      <c r="C98" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="D98" s="3" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="99" spans="2:4">
-      <c r="B99" s="2">
-        <v>3</v>
-      </c>
-      <c r="C99" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="D99" s="3" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="100" spans="2:4">
-      <c r="B100" s="2">
-        <v>3</v>
-      </c>
-      <c r="C100" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="D100" s="3" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="101" spans="2:4">
-      <c r="B101" s="2">
-        <v>3</v>
-      </c>
-      <c r="C101" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="D101" s="3" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="102" spans="2:4">
-      <c r="B102" s="2">
-        <v>3</v>
-      </c>
-      <c r="C102" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="D102" s="3" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="103" spans="2:4">
-      <c r="B103" s="2">
-        <v>3</v>
-      </c>
-      <c r="C103" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="D103" s="3" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="104" spans="2:4">
-      <c r="B104" s="2">
-        <v>3</v>
-      </c>
-      <c r="C104" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="D104" s="3" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="105" spans="2:4">
-      <c r="B105" s="2">
-        <v>3</v>
-      </c>
-      <c r="C105" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="D105" s="3" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="106" spans="2:4">
-      <c r="B106" s="2">
-        <v>3</v>
-      </c>
-      <c r="C106" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="D106" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="108" spans="2:4">
-      <c r="B108" s="2">
-        <v>3</v>
-      </c>
-      <c r="C108" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="D108" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="109" spans="2:4">
-      <c r="B109" s="2">
-        <v>3</v>
-      </c>
-      <c r="C109" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="D109" s="3" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="110" spans="2:4">
-      <c r="B110" s="2">
-        <v>3</v>
-      </c>
-      <c r="C110" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="D110" s="3" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="111" spans="2:4">
-      <c r="B111" s="2">
-        <v>3</v>
-      </c>
-      <c r="C111" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="D111" s="3" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="112" spans="2:4">
-      <c r="B112" s="2">
-        <v>3</v>
-      </c>
-      <c r="C112" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="D112" s="3" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="114" spans="2:4">
-      <c r="B114" s="2">
-        <v>3</v>
-      </c>
-      <c r="C114" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="D114" s="3" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="115" spans="2:4">
-      <c r="B115" s="2">
-        <v>3</v>
-      </c>
-      <c r="C115" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="D115" s="3" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="116" spans="2:4">
-      <c r="B116" s="2">
-        <v>3</v>
-      </c>
-      <c r="C116" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="D116" s="3" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="118" spans="2:4">
-      <c r="B118" s="2">
-        <v>4</v>
-      </c>
-      <c r="C118" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="D118" s="3" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="119" spans="2:4">
-      <c r="B119" s="2">
-        <v>4</v>
-      </c>
-      <c r="C119" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="D119" s="3" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="120" spans="2:4">
-      <c r="B120" s="2">
-        <v>4</v>
-      </c>
-      <c r="C120" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="D120" s="3" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="121" spans="2:4">
-      <c r="B121" s="2">
-        <v>4</v>
-      </c>
-      <c r="C121" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="D121" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="122" spans="2:4">
-      <c r="B122" s="2">
-        <v>4</v>
-      </c>
-      <c r="C122" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="D122" s="3" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="123" spans="2:4">
-      <c r="B123" s="2">
-        <v>4</v>
-      </c>
-      <c r="C123" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="D123" s="3" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="125" spans="2:4">
-      <c r="B125" s="2">
-        <v>4</v>
-      </c>
-      <c r="C125" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="D125" s="3" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="126" spans="2:4">
-      <c r="B126" s="2">
-        <v>4</v>
-      </c>
-      <c r="C126" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="D126" s="3" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="127" spans="2:4">
-      <c r="B127" s="2">
-        <v>4</v>
-      </c>
-      <c r="C127" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="D127" s="3" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="128" spans="2:4">
-      <c r="B128" s="2">
-        <v>4</v>
-      </c>
-      <c r="C128" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="D128" s="3" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="129" spans="2:4">
-      <c r="B129" s="2">
-        <v>4</v>
-      </c>
-      <c r="C129" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="D129" s="3" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="130" spans="2:4">
-      <c r="B130" s="2">
-        <v>4</v>
-      </c>
-      <c r="C130" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="D130" s="3" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="131" spans="2:4">
-      <c r="B131" s="2">
-        <v>4</v>
-      </c>
-      <c r="C131" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="D131" s="3" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="132" spans="2:4">
-      <c r="B132" s="2">
-        <v>4</v>
-      </c>
-      <c r="C132" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="D132" s="3" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="133" spans="2:4">
-      <c r="B133" s="2">
-        <v>4</v>
-      </c>
-      <c r="C133" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="D133" s="3" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="134" spans="2:4">
-      <c r="B134" s="2">
-        <v>4</v>
-      </c>
-      <c r="C134" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="D134" s="3" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="135" spans="2:4">
-      <c r="B135" s="2">
-        <v>4</v>
-      </c>
-      <c r="C135" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="D135" s="3" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="137" spans="2:4">
-      <c r="B137" s="2">
-        <v>4</v>
-      </c>
-      <c r="C137" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="D137" s="3" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="138" spans="2:4">
-      <c r="B138" s="2">
-        <v>4</v>
-      </c>
-      <c r="C138" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="D138" s="3" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="139" spans="2:4">
-      <c r="B139" s="2">
-        <v>4</v>
-      </c>
-      <c r="C139" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="D139" s="3" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="140" spans="2:4">
-      <c r="B140" s="2">
-        <v>4</v>
-      </c>
-      <c r="C140" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="D140" s="3" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="142" spans="2:4">
-      <c r="B142" s="2">
-        <v>4</v>
-      </c>
-      <c r="C142" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="D142" s="3" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="143" spans="2:4">
-      <c r="B143" s="2">
-        <v>4</v>
-      </c>
-      <c r="C143" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="D143" s="3" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="144" spans="2:4">
-      <c r="B144" s="2">
-        <v>4</v>
-      </c>
-      <c r="C144" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="D144" s="3" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="145" spans="2:4">
-      <c r="B145" s="2">
-        <v>4</v>
-      </c>
-      <c r="C145" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="D145" s="3" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="146" spans="2:4">
-      <c r="B146" s="2">
-        <v>4</v>
-      </c>
-      <c r="C146" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="D146" s="3" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="147" spans="2:4">
-      <c r="B147" s="2">
-        <v>4</v>
-      </c>
-      <c r="C147" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="D147" s="3" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="148" spans="2:4">
-      <c r="B148" s="2">
-        <v>4</v>
-      </c>
-      <c r="C148" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="D148" s="3" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="150" spans="2:4">
-      <c r="B150" s="2">
-        <v>4</v>
-      </c>
-      <c r="C150" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="D150" s="3" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="151" spans="2:4">
-      <c r="B151" s="2">
-        <v>4</v>
-      </c>
-      <c r="C151" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="D151" s="3" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="152" spans="2:4">
-      <c r="B152" s="2">
-        <v>4</v>
-      </c>
-      <c r="C152" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="D152" s="3" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="153" spans="2:4">
-      <c r="B153" s="2">
-        <v>4</v>
-      </c>
-      <c r="C153" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="D153" s="3" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="154" spans="2:4">
-      <c r="B154" s="2">
-        <v>4</v>
-      </c>
-      <c r="C154" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="D154" s="3" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="155" spans="2:4">
-      <c r="B155" s="2">
-        <v>4</v>
-      </c>
-      <c r="C155" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="D155" s="3" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="156" spans="2:4">
-      <c r="B156" s="2">
-        <v>4</v>
-      </c>
-      <c r="C156" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="D156" s="3" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="157" spans="2:4">
-      <c r="B157" s="2">
-        <v>4</v>
-      </c>
-      <c r="C157" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="D157" s="3" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="158" spans="2:4">
-      <c r="B158" s="2">
-        <v>4</v>
-      </c>
-      <c r="C158" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="D158" s="3" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="159" spans="2:4">
-      <c r="B159" s="2">
-        <v>4</v>
-      </c>
-      <c r="C159" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="D159" s="3" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="161" spans="2:4">
-      <c r="B161" s="2">
+    <row r="176" spans="2:5">
+      <c r="B176">
         <v>5</v>
       </c>
-      <c r="C161" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="D161" s="3" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="162" spans="2:4">
-      <c r="B162" s="2">
+      <c r="D176" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="E176" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="177" spans="2:5">
+      <c r="B177">
         <v>5</v>
       </c>
-      <c r="C162" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="D162" s="3" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="163" spans="2:4">
-      <c r="B163" s="2">
+      <c r="D177" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="E177" s="2" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="178" spans="2:5">
+      <c r="B178">
         <v>5</v>
       </c>
-      <c r="C163" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="D163" s="3" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="164" spans="2:4">
-      <c r="B164" s="2">
+      <c r="D178" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="E178" s="2" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="179" spans="2:5">
+      <c r="B179">
         <v>5</v>
       </c>
-      <c r="C164" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="D164" s="3" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="165" spans="2:4">
-      <c r="B165" s="2">
+      <c r="D179" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="E179" s="2" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="180" spans="2:5">
+      <c r="B180">
         <v>5</v>
       </c>
-      <c r="C165" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="D165" s="3" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="166" spans="2:4">
-      <c r="B166" s="2">
+      <c r="D180" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="E180" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="181" spans="2:5">
+      <c r="B181">
         <v>5</v>
       </c>
-      <c r="C166" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="D166" s="3" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="167" spans="2:4">
-      <c r="B167" s="2">
+      <c r="D181" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="E181" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="182" spans="2:5">
+      <c r="B182">
         <v>5</v>
       </c>
-      <c r="C167" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="D167" s="3" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="169" spans="2:4">
-      <c r="B169" s="2">
+      <c r="D182" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="E182" s="2" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="184" spans="2:5">
+      <c r="B184">
         <v>5</v>
       </c>
-      <c r="C169" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="D169" s="3" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="170" spans="2:4">
-      <c r="B170" s="2">
+      <c r="D184" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="E184" s="2" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="185" spans="2:5">
+      <c r="B185">
         <v>5</v>
       </c>
-      <c r="C170" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="D170" s="3" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="171" spans="2:4">
-      <c r="B171" s="2">
+      <c r="D185" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="E185" s="2" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="186" spans="2:5">
+      <c r="B186">
         <v>5</v>
       </c>
-      <c r="C171" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="D171" s="3" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="172" spans="2:4">
-      <c r="B172" s="2">
+      <c r="D186" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="E186" s="2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="187" spans="2:5">
+      <c r="B187">
         <v>5</v>
       </c>
-      <c r="C172" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="D172" s="3" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="173" spans="2:4">
-      <c r="B173" s="2">
+      <c r="D187" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="E187" s="2" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="188" spans="2:5">
+      <c r="B188">
         <v>5</v>
       </c>
-      <c r="C173" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="D173" s="3" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="175" spans="2:4">
-      <c r="B175" s="2">
+      <c r="D188" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="E188" s="2" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="189" spans="2:5">
+      <c r="B189">
         <v>5</v>
       </c>
-      <c r="C175" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="D175" s="3" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="176" spans="2:4">
-      <c r="B176" s="2">
+      <c r="D189" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="E189" s="2" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="190" spans="2:5">
+      <c r="B190">
         <v>5</v>
       </c>
-      <c r="C176" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="D176" s="3" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="177" spans="2:4">
-      <c r="B177" s="2">
+      <c r="D190" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="E190" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="191" spans="2:5">
+      <c r="B191">
         <v>5</v>
       </c>
-      <c r="C177" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="D177" s="3" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="178" spans="2:4">
-      <c r="B178" s="2">
-        <v>5</v>
-      </c>
-      <c r="C178" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="D178" s="3" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="179" spans="2:4">
-      <c r="B179" s="2">
-        <v>5</v>
-      </c>
-      <c r="C179" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="D179" s="3" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="180" spans="2:4">
-      <c r="B180" s="2">
-        <v>5</v>
-      </c>
-      <c r="C180" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="D180" s="3" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="181" spans="2:4">
-      <c r="B181" s="2">
-        <v>5</v>
-      </c>
-      <c r="C181" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="D181" s="3" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="182" spans="2:4">
-      <c r="B182" s="2">
-        <v>5</v>
-      </c>
-      <c r="C182" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="D182" s="3" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="184" spans="2:4">
-      <c r="B184" s="2">
-        <v>5</v>
-      </c>
-      <c r="C184" s="4" t="s">
+      <c r="D191" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="D184" s="3" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="185" spans="2:4">
-      <c r="B185" s="2">
-        <v>5</v>
-      </c>
-      <c r="C185" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="D185" s="3" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="186" spans="2:4">
-      <c r="B186" s="2">
-        <v>5</v>
-      </c>
-      <c r="C186" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="D186" s="3" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="187" spans="2:4">
-      <c r="B187" s="2">
-        <v>5</v>
-      </c>
-      <c r="C187" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="D187" s="3" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="188" spans="2:4">
-      <c r="B188" s="2">
-        <v>5</v>
-      </c>
-      <c r="C188" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="D188" s="3" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="189" spans="2:4">
-      <c r="B189" s="2">
-        <v>5</v>
-      </c>
-      <c r="C189" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="D189" s="3" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="190" spans="2:4">
-      <c r="B190" s="2">
-        <v>5</v>
-      </c>
-      <c r="C190" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="D190" s="3" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="191" spans="2:4">
-      <c r="B191" s="2">
-        <v>5</v>
-      </c>
-      <c r="C191" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="D191" s="3" t="s">
+      <c r="E191" s="2" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="193" spans="3:4">
-      <c r="C193" s="7"/>
-      <c r="D193" s="8"/>
+    <row r="193" spans="4:5">
+      <c r="D193" s="6"/>
+      <c r="E193" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>

--- a/Tasks.xlsx
+++ b/Tasks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pas02\Nextcloud\Documents\03_Data Science - Uni Stuttgart\06_SoS 2026\04_Software Engineering\Group project 3\ai-travel-planner\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B71A8C57-1159-469E-9F91-6C2F66974ADF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{154FF6F2-CCE5-4BF7-A676-CE7AE4DD9DB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{834F46D4-8CFA-4605-9F2C-653FA769D6F4}"/>
   </bookViews>
@@ -1074,7 +1074,7 @@
                   <c:v>137</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>137</c:v>
+                  <c:v>112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2447,7 +2447,7 @@
       </c>
       <c r="J7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K7">
         <f t="shared" ref="K7:K10" si="2">K6-I7</f>
@@ -2455,11 +2455,11 @@
       </c>
       <c r="L7">
         <f t="shared" ref="L7:L10" si="3">IF(H7&gt;$L$3,"",L6-J7)</f>
-        <v>137</v>
+        <v>112</v>
       </c>
       <c r="M7">
         <f>IF(H7&gt;$L$3,"",L7)</f>
-        <v>137</v>
+        <v>112</v>
       </c>
     </row>
     <row r="8" spans="2:13">
@@ -3046,6 +3046,9 @@
       <c r="E42" s="2" t="s">
         <v>35</v>
       </c>
+      <c r="F42">
+        <v>2</v>
+      </c>
     </row>
     <row r="43" spans="2:6">
       <c r="B43">
@@ -3060,6 +3063,9 @@
       <c r="E43" s="2" t="s">
         <v>36</v>
       </c>
+      <c r="F43">
+        <v>2</v>
+      </c>
     </row>
     <row r="44" spans="2:6">
       <c r="B44">
@@ -3074,6 +3080,9 @@
       <c r="E44" s="2" t="s">
         <v>37</v>
       </c>
+      <c r="F44">
+        <v>2</v>
+      </c>
     </row>
     <row r="45" spans="2:6">
       <c r="B45">
@@ -3088,6 +3097,9 @@
       <c r="E45" s="2" t="s">
         <v>38</v>
       </c>
+      <c r="F45">
+        <v>2</v>
+      </c>
     </row>
     <row r="46" spans="2:6">
       <c r="B46">
@@ -3102,6 +3114,9 @@
       <c r="E46" s="2" t="s">
         <v>39</v>
       </c>
+      <c r="F46">
+        <v>2</v>
+      </c>
     </row>
     <row r="47" spans="2:6">
       <c r="B47">
@@ -3116,6 +3131,9 @@
       <c r="E47" s="2" t="s">
         <v>40</v>
       </c>
+      <c r="F47">
+        <v>2</v>
+      </c>
     </row>
     <row r="48" spans="2:6">
       <c r="B48">
@@ -3130,8 +3148,11 @@
       <c r="E48" s="2" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="50" spans="2:5">
+      <c r="F48">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50" spans="2:6">
       <c r="B50">
         <v>2</v>
       </c>
@@ -3144,8 +3165,11 @@
       <c r="E50" s="2" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="51" spans="2:5">
+      <c r="F50">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51" spans="2:6">
       <c r="B51">
         <v>2</v>
       </c>
@@ -3158,8 +3182,11 @@
       <c r="E51" s="2" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="52" spans="2:5">
+      <c r="F51">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="52" spans="2:6">
       <c r="B52">
         <v>2</v>
       </c>
@@ -3172,8 +3199,11 @@
       <c r="E52" s="2" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="53" spans="2:5">
+      <c r="F52">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53" spans="2:6">
       <c r="B53">
         <v>2</v>
       </c>
@@ -3186,8 +3216,11 @@
       <c r="E53" s="2" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="54" spans="2:5">
+      <c r="F53">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54" spans="2:6">
       <c r="B54">
         <v>2</v>
       </c>
@@ -3200,8 +3233,11 @@
       <c r="E54" s="2" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="55" spans="2:5">
+      <c r="F54">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55" spans="2:6">
       <c r="B55">
         <v>2</v>
       </c>
@@ -3214,8 +3250,11 @@
       <c r="E55" s="2" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="57" spans="2:5">
+      <c r="F55">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="57" spans="2:6">
       <c r="B57">
         <v>2</v>
       </c>
@@ -3228,8 +3267,11 @@
       <c r="E57" s="2" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="58" spans="2:5">
+      <c r="F57">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="58" spans="2:6">
       <c r="B58">
         <v>2</v>
       </c>
@@ -3242,8 +3284,11 @@
       <c r="E58" s="2" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="59" spans="2:5">
+      <c r="F58">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="59" spans="2:6">
       <c r="B59">
         <v>2</v>
       </c>
@@ -3256,8 +3301,11 @@
       <c r="E59" s="2" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="60" spans="2:5">
+      <c r="F59">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="60" spans="2:6">
       <c r="B60">
         <v>2</v>
       </c>
@@ -3270,8 +3318,11 @@
       <c r="E60" s="2" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="61" spans="2:5">
+      <c r="F60">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="61" spans="2:6">
       <c r="B61">
         <v>2</v>
       </c>
@@ -3284,8 +3335,11 @@
       <c r="E61" s="2" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="62" spans="2:5">
+      <c r="F61">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="62" spans="2:6">
       <c r="B62">
         <v>2</v>
       </c>
@@ -3298,8 +3352,11 @@
       <c r="E62" s="2" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="64" spans="2:5">
+      <c r="F62">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="64" spans="2:6">
       <c r="B64">
         <v>2</v>
       </c>
@@ -3312,8 +3369,11 @@
       <c r="E64" s="2" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="65" spans="2:5">
+      <c r="F64">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="65" spans="2:6">
       <c r="B65">
         <v>2</v>
       </c>
@@ -3326,8 +3386,11 @@
       <c r="E65" s="2" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="66" spans="2:5">
+      <c r="F65">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="66" spans="2:6">
       <c r="B66">
         <v>2</v>
       </c>
@@ -3340,8 +3403,11 @@
       <c r="E66" s="2" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="67" spans="2:5">
+      <c r="F66">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="67" spans="2:6">
       <c r="B67">
         <v>2</v>
       </c>
@@ -3354,8 +3420,11 @@
       <c r="E67" s="2" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="68" spans="2:5">
+      <c r="F67">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="68" spans="2:6">
       <c r="B68">
         <v>2</v>
       </c>
@@ -3368,8 +3437,11 @@
       <c r="E68" s="2" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="69" spans="2:5">
+      <c r="F68">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="69" spans="2:6">
       <c r="B69">
         <v>2</v>
       </c>
@@ -3382,8 +3454,11 @@
       <c r="E69" s="2" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="71" spans="2:5">
+      <c r="F69">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="71" spans="2:6">
       <c r="B71">
         <v>2</v>
       </c>
@@ -3397,7 +3472,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="72" spans="2:5">
+    <row r="72" spans="2:6">
       <c r="B72">
         <v>2</v>
       </c>
@@ -3411,7 +3486,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="73" spans="2:5">
+    <row r="73" spans="2:6">
       <c r="B73">
         <v>2</v>
       </c>
@@ -3425,7 +3500,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="74" spans="2:5">
+    <row r="74" spans="2:6">
       <c r="B74">
         <v>2</v>
       </c>
@@ -3439,7 +3514,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="75" spans="2:5">
+    <row r="75" spans="2:6">
       <c r="B75">
         <v>2</v>
       </c>
@@ -3453,7 +3528,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="76" spans="2:5">
+    <row r="76" spans="2:6">
       <c r="B76">
         <v>2</v>
       </c>
@@ -3467,7 +3542,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="77" spans="2:5">
+    <row r="77" spans="2:6">
       <c r="B77">
         <v>2</v>
       </c>
@@ -3481,7 +3556,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="78" spans="2:5">
+    <row r="78" spans="2:6">
       <c r="B78">
         <v>2</v>
       </c>
@@ -3495,7 +3570,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:5">
+    <row r="80" spans="2:6">
       <c r="B80">
         <v>3</v>
       </c>

--- a/Tasks.xlsx
+++ b/Tasks.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11130"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pas02\Nextcloud\Documents\03_Data Science - Uni Stuttgart\06_SoS 2026\04_Software Engineering\Group project 3\ai-travel-planner\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jacopodonati/Documents/PROGETTI/TRAVELMINDER/ai-travel-planner/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{154FF6F2-CCE5-4BF7-A676-CE7AE4DD9DB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC8C1117-651F-C448-AF2C-887FE43AEF47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{834F46D4-8CFA-4605-9F2C-653FA769D6F4}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="33600" windowHeight="18860" xr2:uid="{834F46D4-8CFA-4605-9F2C-653FA769D6F4}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -595,6 +595,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
       </rPr>
       <t>.env.example</t>
     </r>
@@ -608,6 +609,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
       </rPr>
       <t>/api/generate</t>
     </r>
@@ -631,6 +633,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
       </rPr>
       <t>/api/regen</t>
     </r>
@@ -654,6 +657,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
       </rPr>
       <t>promptBuilder.js</t>
     </r>
@@ -667,6 +671,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
       </rPr>
       <t>/api/generate</t>
     </r>
@@ -690,6 +695,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
       </rPr>
       <t>/api/regen</t>
     </r>
@@ -757,7 +763,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -777,6 +783,7 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial Unicode MS"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="16"/>
@@ -837,7 +844,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -855,7 +862,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="de-DE"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1074,7 +1081,7 @@
                   <c:v>137</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>112</c:v>
+                  <c:v>104</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1977,7 +1984,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -2294,16 +2301,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67F1D602-D536-4BC9-865A-CD2C06CAE9C2}">
   <dimension ref="B2:M193"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="6.85546875" customWidth="1"/>
-    <col min="3" max="3" width="22.85546875" customWidth="1"/>
-    <col min="4" max="4" width="29.7109375" customWidth="1"/>
-    <col min="5" max="5" width="66.140625" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" customWidth="1"/>
+    <col min="2" max="2" width="6.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+    <col min="4" max="4" width="29.6640625" customWidth="1"/>
+    <col min="5" max="5" width="66.1640625" customWidth="1"/>
+    <col min="6" max="6" width="12.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:13" ht="21">
+    <row r="2" spans="2:13" ht="22" x14ac:dyDescent="0.3">
       <c r="B2" s="5" t="s">
         <v>191</v>
       </c>
@@ -2312,7 +2319,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="3" spans="2:13">
+    <row r="3" spans="2:13" x14ac:dyDescent="0.2">
       <c r="E3" s="4"/>
       <c r="K3" t="s">
         <v>199</v>
@@ -2321,7 +2328,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="2:13">
+    <row r="4" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B4" s="1" t="s">
         <v>188</v>
       </c>
@@ -2353,7 +2360,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="5" spans="2:13">
+    <row r="5" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B5">
         <v>1</v>
       </c>
@@ -2376,7 +2383,7 @@
         <v>0</v>
       </c>
       <c r="J5">
-        <f>COUNTIF($F$5:$F$192,H5)</f>
+        <f>COUNTIF($F$5:$F$199,H5)</f>
         <v>0</v>
       </c>
       <c r="K5">
@@ -2386,7 +2393,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="6" spans="2:13">
+    <row r="6" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B6">
         <v>1</v>
       </c>
@@ -2410,7 +2417,7 @@
         <v>33</v>
       </c>
       <c r="J6">
-        <f t="shared" ref="J6:J10" si="0">COUNTIF($F$5:$F$192,H6)</f>
+        <f>COUNTIF($F$5:$F$199,H6)</f>
         <v>28</v>
       </c>
       <c r="K6">
@@ -2422,7 +2429,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="7" spans="2:13">
+    <row r="7" spans="2:13" ht="17" x14ac:dyDescent="0.2">
       <c r="B7">
         <v>1</v>
       </c>
@@ -2442,27 +2449,27 @@
         <v>2</v>
       </c>
       <c r="I7">
-        <f t="shared" ref="I7:I10" si="1">COUNTIF($B$5:$B$1900,H7)</f>
+        <f t="shared" ref="I7:I10" si="0">COUNTIF($B$5:$B$1900,H7)</f>
         <v>33</v>
       </c>
       <c r="J7">
-        <f t="shared" si="0"/>
-        <v>25</v>
+        <f>COUNTIF($F$5:$F$199,H7)</f>
+        <v>33</v>
       </c>
       <c r="K7">
-        <f t="shared" ref="K7:K10" si="2">K6-I7</f>
+        <f t="shared" ref="K7:K10" si="1">K6-I7</f>
         <v>99</v>
       </c>
       <c r="L7">
-        <f t="shared" ref="L7:L10" si="3">IF(H7&gt;$L$3,"",L6-J7)</f>
-        <v>112</v>
+        <f t="shared" ref="L7:L10" si="2">IF(H7&gt;$L$3,"",L6-J7)</f>
+        <v>104</v>
       </c>
       <c r="M7">
         <f>IF(H7&gt;$L$3,"",L7)</f>
-        <v>112</v>
-      </c>
-    </row>
-    <row r="8" spans="2:13">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="8" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B8">
         <v>1</v>
       </c>
@@ -2482,19 +2489,19 @@
         <v>3</v>
       </c>
       <c r="I8">
+        <f t="shared" si="0"/>
+        <v>33</v>
+      </c>
+      <c r="J8">
+        <f>COUNTIF($F$5:$F$199,H8)</f>
+        <v>0</v>
+      </c>
+      <c r="K8">
         <f t="shared" si="1"/>
-        <v>33</v>
-      </c>
-      <c r="J8">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K8">
+        <v>66</v>
+      </c>
+      <c r="L8" t="str">
         <f t="shared" si="2"/>
-        <v>66</v>
-      </c>
-      <c r="L8" t="str">
-        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="M8" t="str">
@@ -2502,7 +2509,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="2:13">
+    <row r="9" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B9">
         <v>1</v>
       </c>
@@ -2522,19 +2529,19 @@
         <v>4</v>
       </c>
       <c r="I9">
+        <f t="shared" si="0"/>
+        <v>38</v>
+      </c>
+      <c r="J9">
+        <f>COUNTIF($F$5:$F$199,H9)</f>
+        <v>0</v>
+      </c>
+      <c r="K9">
         <f t="shared" si="1"/>
-        <v>38</v>
-      </c>
-      <c r="J9">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K9">
+        <v>28</v>
+      </c>
+      <c r="L9" t="str">
         <f t="shared" si="2"/>
-        <v>28</v>
-      </c>
-      <c r="L9" t="str">
-        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="M9" t="str">
@@ -2542,7 +2549,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="2:13">
+    <row r="10" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B10">
         <v>1</v>
       </c>
@@ -2562,19 +2569,19 @@
         <v>5</v>
       </c>
       <c r="I10">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="J10">
+        <f>COUNTIF($F$5:$F$199,H10)</f>
+        <v>0</v>
+      </c>
+      <c r="K10">
         <f t="shared" si="1"/>
-        <v>28</v>
-      </c>
-      <c r="J10">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K10">
+      <c r="L10" t="str">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L10" t="str">
-        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="M10" t="str">
@@ -2582,7 +2589,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="2:13">
+    <row r="11" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B11">
         <v>1</v>
       </c>
@@ -2606,7 +2613,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="12" spans="2:13">
+    <row r="12" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B12">
         <v>1</v>
       </c>
@@ -2623,7 +2630,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="2:13">
+    <row r="14" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B14">
         <v>1</v>
       </c>
@@ -2640,7 +2647,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="2:13">
+    <row r="15" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B15">
         <v>1</v>
       </c>
@@ -2657,7 +2664,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="2:13">
+    <row r="16" spans="2:13" ht="17" x14ac:dyDescent="0.2">
       <c r="B16">
         <v>1</v>
       </c>
@@ -2674,7 +2681,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="2:6">
+    <row r="17" spans="2:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B17">
         <v>1</v>
       </c>
@@ -2691,7 +2698,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="2:6">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B18">
         <v>1</v>
       </c>
@@ -2708,7 +2715,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="2:6">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B19">
         <v>1</v>
       </c>
@@ -2725,7 +2732,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="2:6">
+    <row r="20" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B20">
         <v>1</v>
       </c>
@@ -2742,7 +2749,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="2:6">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22">
         <v>1</v>
       </c>
@@ -2759,7 +2766,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="2:6">
+    <row r="23" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B23">
         <v>1</v>
       </c>
@@ -2776,7 +2783,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="2:6">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B24">
         <v>1</v>
       </c>
@@ -2793,7 +2800,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="2:6">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B25">
         <v>1</v>
       </c>
@@ -2810,7 +2817,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="2:6">
+    <row r="26" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B26">
         <v>1</v>
       </c>
@@ -2827,7 +2834,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="2:6">
+    <row r="27" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B27">
         <v>1</v>
       </c>
@@ -2844,7 +2851,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="2:6">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B28">
         <v>1</v>
       </c>
@@ -2861,7 +2868,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="2:6">
+    <row r="29" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B29">
         <v>1</v>
       </c>
@@ -2878,7 +2885,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="2:6">
+    <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30">
         <v>1</v>
       </c>
@@ -2895,7 +2902,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="2:6">
+    <row r="31" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B31">
         <v>1</v>
       </c>
@@ -2912,7 +2919,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="2:6">
+    <row r="32" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B32">
         <v>1</v>
       </c>
@@ -2929,7 +2936,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="2:6">
+    <row r="33" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B33">
         <v>1</v>
       </c>
@@ -2946,7 +2953,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="2:6">
+    <row r="34" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B34">
         <v>1</v>
       </c>
@@ -2963,7 +2970,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="2:6">
+    <row r="36" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B36">
         <v>1</v>
       </c>
@@ -2977,7 +2984,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="37" spans="2:6">
+    <row r="37" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B37">
         <v>1</v>
       </c>
@@ -2991,7 +2998,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:6">
+    <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38">
         <v>1</v>
       </c>
@@ -3005,7 +3012,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="39" spans="2:6">
+    <row r="39" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B39">
         <v>1</v>
       </c>
@@ -3019,7 +3026,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="40" spans="2:6">
+    <row r="40" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B40">
         <v>1</v>
       </c>
@@ -3033,7 +3040,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="42" spans="2:6">
+    <row r="42" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B42">
         <v>2</v>
       </c>
@@ -3050,7 +3057,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="43" spans="2:6">
+    <row r="43" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B43">
         <v>2</v>
       </c>
@@ -3067,7 +3074,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="44" spans="2:6">
+    <row r="44" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B44">
         <v>2</v>
       </c>
@@ -3084,7 +3091,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="45" spans="2:6">
+    <row r="45" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B45">
         <v>2</v>
       </c>
@@ -3101,7 +3108,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="46" spans="2:6">
+    <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46">
         <v>2</v>
       </c>
@@ -3118,7 +3125,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="47" spans="2:6">
+    <row r="47" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B47">
         <v>2</v>
       </c>
@@ -3135,7 +3142,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="48" spans="2:6">
+    <row r="48" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B48">
         <v>2</v>
       </c>
@@ -3152,7 +3159,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="2:6">
+    <row r="50" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B50">
         <v>2</v>
       </c>
@@ -3169,7 +3176,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="51" spans="2:6">
+    <row r="51" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B51">
         <v>2</v>
       </c>
@@ -3186,7 +3193,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="52" spans="2:6">
+    <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52">
         <v>2</v>
       </c>
@@ -3203,7 +3210,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="53" spans="2:6">
+    <row r="53" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B53">
         <v>2</v>
       </c>
@@ -3220,7 +3227,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="2:6">
+    <row r="54" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B54">
         <v>2</v>
       </c>
@@ -3237,7 +3244,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="55" spans="2:6">
+    <row r="55" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B55">
         <v>2</v>
       </c>
@@ -3254,7 +3261,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="57" spans="2:6">
+    <row r="57" spans="2:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B57">
         <v>2</v>
       </c>
@@ -3271,7 +3278,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="58" spans="2:6">
+    <row r="58" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B58">
         <v>2</v>
       </c>
@@ -3288,7 +3295,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="59" spans="2:6">
+    <row r="59" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B59">
         <v>2</v>
       </c>
@@ -3305,7 +3312,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="60" spans="2:6">
+    <row r="60" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B60">
         <v>2</v>
       </c>
@@ -3322,7 +3329,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="61" spans="2:6">
+    <row r="61" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B61">
         <v>2</v>
       </c>
@@ -3339,7 +3346,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="62" spans="2:6">
+    <row r="62" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B62">
         <v>2</v>
       </c>
@@ -3356,7 +3363,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="64" spans="2:6">
+    <row r="64" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B64">
         <v>2</v>
       </c>
@@ -3373,7 +3380,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="65" spans="2:6">
+    <row r="65" spans="2:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B65">
         <v>2</v>
       </c>
@@ -3390,7 +3397,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="66" spans="2:6">
+    <row r="66" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B66">
         <v>2</v>
       </c>
@@ -3407,7 +3414,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="67" spans="2:6">
+    <row r="67" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B67">
         <v>2</v>
       </c>
@@ -3424,7 +3431,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="68" spans="2:6">
+    <row r="68" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B68">
         <v>2</v>
       </c>
@@ -3441,7 +3448,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="69" spans="2:6">
+    <row r="69" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B69">
         <v>2</v>
       </c>
@@ -3458,7 +3465,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="71" spans="2:6">
+    <row r="71" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B71">
         <v>2</v>
       </c>
@@ -3471,8 +3478,11 @@
       <c r="E71" s="2" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="72" spans="2:6">
+      <c r="F71">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="72" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B72">
         <v>2</v>
       </c>
@@ -3485,8 +3495,11 @@
       <c r="E72" s="2" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="73" spans="2:6">
+      <c r="F72">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="73" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B73">
         <v>2</v>
       </c>
@@ -3499,8 +3512,11 @@
       <c r="E73" s="2" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="74" spans="2:6">
+      <c r="F73">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="74" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B74">
         <v>2</v>
       </c>
@@ -3513,8 +3529,11 @@
       <c r="E74" s="2" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="75" spans="2:6">
+      <c r="F74">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="75" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B75">
         <v>2</v>
       </c>
@@ -3527,8 +3546,11 @@
       <c r="E75" s="2" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="76" spans="2:6">
+      <c r="F75">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="76" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B76">
         <v>2</v>
       </c>
@@ -3541,8 +3563,11 @@
       <c r="E76" s="2" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="77" spans="2:6">
+      <c r="F76">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="77" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B77">
         <v>2</v>
       </c>
@@ -3555,8 +3580,11 @@
       <c r="E77" s="2" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="78" spans="2:6">
+      <c r="F77">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="78" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B78">
         <v>2</v>
       </c>
@@ -3569,8 +3597,11 @@
       <c r="E78" s="2" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="80" spans="2:6">
+      <c r="F78">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="80" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B80">
         <v>3</v>
       </c>
@@ -3581,7 +3612,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="81" spans="2:5">
+    <row r="81" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B81">
         <v>3</v>
       </c>
@@ -3592,7 +3623,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="82" spans="2:5">
+    <row r="82" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B82">
         <v>3</v>
       </c>
@@ -3603,7 +3634,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="83" spans="2:5">
+    <row r="83" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B83">
         <v>3</v>
       </c>
@@ -3614,7 +3645,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="85" spans="2:5">
+    <row r="85" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B85">
         <v>3</v>
       </c>
@@ -3625,7 +3656,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="86" spans="2:5">
+    <row r="86" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B86">
         <v>3</v>
       </c>
@@ -3636,7 +3667,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="87" spans="2:5">
+    <row r="87" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B87">
         <v>3</v>
       </c>
@@ -3647,7 +3678,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="88" spans="2:5">
+    <row r="88" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B88">
         <v>3</v>
       </c>
@@ -3658,7 +3689,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="89" spans="2:5">
+    <row r="89" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B89">
         <v>3</v>
       </c>
@@ -3669,7 +3700,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="90" spans="2:5">
+    <row r="90" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B90">
         <v>3</v>
       </c>
@@ -3680,7 +3711,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="91" spans="2:5">
+    <row r="91" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B91">
         <v>3</v>
       </c>
@@ -3691,7 +3722,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="92" spans="2:5">
+    <row r="92" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B92">
         <v>3</v>
       </c>
@@ -3702,7 +3733,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="93" spans="2:5">
+    <row r="93" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B93">
         <v>3</v>
       </c>
@@ -3713,7 +3744,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="94" spans="2:5">
+    <row r="94" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B94">
         <v>3</v>
       </c>
@@ -3724,7 +3755,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="95" spans="2:5">
+    <row r="95" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B95">
         <v>3</v>
       </c>
@@ -3735,7 +3766,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="97" spans="2:5">
+    <row r="97" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B97">
         <v>3</v>
       </c>
@@ -3746,7 +3777,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="98" spans="2:5">
+    <row r="98" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B98">
         <v>3</v>
       </c>
@@ -3757,7 +3788,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="99" spans="2:5">
+    <row r="99" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B99">
         <v>3</v>
       </c>
@@ -3768,7 +3799,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="100" spans="2:5">
+    <row r="100" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B100">
         <v>3</v>
       </c>
@@ -3779,7 +3810,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="101" spans="2:5">
+    <row r="101" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B101">
         <v>3</v>
       </c>
@@ -3790,7 +3821,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="102" spans="2:5">
+    <row r="102" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B102">
         <v>3</v>
       </c>
@@ -3801,7 +3832,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="103" spans="2:5">
+    <row r="103" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B103">
         <v>3</v>
       </c>
@@ -3812,7 +3843,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="104" spans="2:5">
+    <row r="104" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B104">
         <v>3</v>
       </c>
@@ -3823,7 +3854,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="105" spans="2:5">
+    <row r="105" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B105">
         <v>3</v>
       </c>
@@ -3834,7 +3865,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="106" spans="2:5">
+    <row r="106" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B106">
         <v>3</v>
       </c>
@@ -3845,7 +3876,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="108" spans="2:5">
+    <row r="108" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B108">
         <v>3</v>
       </c>
@@ -3856,7 +3887,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="109" spans="2:5">
+    <row r="109" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B109">
         <v>3</v>
       </c>
@@ -3867,7 +3898,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="110" spans="2:5">
+    <row r="110" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B110">
         <v>3</v>
       </c>
@@ -3878,7 +3909,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="111" spans="2:5">
+    <row r="111" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B111">
         <v>3</v>
       </c>
@@ -3889,7 +3920,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="112" spans="2:5">
+    <row r="112" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B112">
         <v>3</v>
       </c>
@@ -3900,7 +3931,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="114" spans="2:5">
+    <row r="114" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B114">
         <v>3</v>
       </c>
@@ -3911,7 +3942,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="115" spans="2:5">
+    <row r="115" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B115">
         <v>3</v>
       </c>
@@ -3922,7 +3953,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="116" spans="2:5">
+    <row r="116" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B116">
         <v>3</v>
       </c>
@@ -3933,7 +3964,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="118" spans="2:5">
+    <row r="118" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B118">
         <v>4</v>
       </c>
@@ -3944,7 +3975,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="119" spans="2:5">
+    <row r="119" spans="2:5" ht="17" x14ac:dyDescent="0.2">
       <c r="B119">
         <v>4</v>
       </c>
@@ -3955,7 +3986,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="120" spans="2:5">
+    <row r="120" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B120">
         <v>4</v>
       </c>
@@ -3966,7 +3997,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="121" spans="2:5">
+    <row r="121" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B121">
         <v>4</v>
       </c>
@@ -3977,7 +4008,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="122" spans="2:5">
+    <row r="122" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B122">
         <v>4</v>
       </c>
@@ -3988,7 +4019,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="123" spans="2:5">
+    <row r="123" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B123">
         <v>4</v>
       </c>
@@ -3999,7 +4030,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="125" spans="2:5">
+    <row r="125" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B125">
         <v>4</v>
       </c>
@@ -4010,7 +4041,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="126" spans="2:5">
+    <row r="126" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B126">
         <v>4</v>
       </c>
@@ -4021,7 +4052,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="127" spans="2:5">
+    <row r="127" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B127">
         <v>4</v>
       </c>
@@ -4032,7 +4063,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="128" spans="2:5">
+    <row r="128" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B128">
         <v>4</v>
       </c>
@@ -4043,7 +4074,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="129" spans="2:5">
+    <row r="129" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B129">
         <v>4</v>
       </c>
@@ -4054,7 +4085,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="130" spans="2:5">
+    <row r="130" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B130">
         <v>4</v>
       </c>
@@ -4065,7 +4096,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="131" spans="2:5">
+    <row r="131" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B131">
         <v>4</v>
       </c>
@@ -4076,7 +4107,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="132" spans="2:5">
+    <row r="132" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B132">
         <v>4</v>
       </c>
@@ -4087,7 +4118,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="133" spans="2:5">
+    <row r="133" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B133">
         <v>4</v>
       </c>
@@ -4098,7 +4129,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="134" spans="2:5">
+    <row r="134" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B134">
         <v>4</v>
       </c>
@@ -4109,7 +4140,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="135" spans="2:5">
+    <row r="135" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B135">
         <v>4</v>
       </c>
@@ -4120,7 +4151,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="137" spans="2:5">
+    <row r="137" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B137">
         <v>4</v>
       </c>
@@ -4131,7 +4162,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="138" spans="2:5">
+    <row r="138" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B138">
         <v>4</v>
       </c>
@@ -4142,7 +4173,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="139" spans="2:5">
+    <row r="139" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B139">
         <v>4</v>
       </c>
@@ -4153,7 +4184,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="140" spans="2:5">
+    <row r="140" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B140">
         <v>4</v>
       </c>
@@ -4164,7 +4195,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="142" spans="2:5">
+    <row r="142" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B142">
         <v>4</v>
       </c>
@@ -4175,7 +4206,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="143" spans="2:5">
+    <row r="143" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B143">
         <v>4</v>
       </c>
@@ -4186,7 +4217,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="144" spans="2:5">
+    <row r="144" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B144">
         <v>4</v>
       </c>
@@ -4197,7 +4228,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="145" spans="2:5">
+    <row r="145" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B145">
         <v>4</v>
       </c>
@@ -4208,7 +4239,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="146" spans="2:5">
+    <row r="146" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B146">
         <v>4</v>
       </c>
@@ -4219,7 +4250,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="147" spans="2:5">
+    <row r="147" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B147">
         <v>4</v>
       </c>
@@ -4230,7 +4261,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="148" spans="2:5">
+    <row r="148" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B148">
         <v>4</v>
       </c>
@@ -4241,7 +4272,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="150" spans="2:5">
+    <row r="150" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B150">
         <v>4</v>
       </c>
@@ -4252,7 +4283,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="151" spans="2:5">
+    <row r="151" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B151">
         <v>4</v>
       </c>
@@ -4263,7 +4294,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="152" spans="2:5">
+    <row r="152" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B152">
         <v>4</v>
       </c>
@@ -4274,7 +4305,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="153" spans="2:5">
+    <row r="153" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B153">
         <v>4</v>
       </c>
@@ -4285,7 +4316,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="154" spans="2:5">
+    <row r="154" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B154">
         <v>4</v>
       </c>
@@ -4296,7 +4327,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="155" spans="2:5">
+    <row r="155" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B155">
         <v>4</v>
       </c>
@@ -4307,7 +4338,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="156" spans="2:5">
+    <row r="156" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B156">
         <v>4</v>
       </c>
@@ -4318,7 +4349,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="157" spans="2:5">
+    <row r="157" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B157">
         <v>4</v>
       </c>
@@ -4329,7 +4360,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="158" spans="2:5">
+    <row r="158" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B158">
         <v>4</v>
       </c>
@@ -4340,7 +4371,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="159" spans="2:5">
+    <row r="159" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B159">
         <v>4</v>
       </c>
@@ -4351,7 +4382,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="161" spans="2:5">
+    <row r="161" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B161">
         <v>5</v>
       </c>
@@ -4362,7 +4393,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="162" spans="2:5">
+    <row r="162" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B162">
         <v>5</v>
       </c>
@@ -4373,7 +4404,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="163" spans="2:5">
+    <row r="163" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B163">
         <v>5</v>
       </c>
@@ -4384,7 +4415,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="164" spans="2:5">
+    <row r="164" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B164">
         <v>5</v>
       </c>
@@ -4395,7 +4426,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="165" spans="2:5">
+    <row r="165" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B165">
         <v>5</v>
       </c>
@@ -4406,7 +4437,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="166" spans="2:5">
+    <row r="166" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B166">
         <v>5</v>
       </c>
@@ -4417,7 +4448,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="167" spans="2:5">
+    <row r="167" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B167">
         <v>5</v>
       </c>
@@ -4428,7 +4459,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="169" spans="2:5">
+    <row r="169" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B169">
         <v>5</v>
       </c>
@@ -4439,7 +4470,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="170" spans="2:5">
+    <row r="170" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B170">
         <v>5</v>
       </c>
@@ -4450,7 +4481,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="171" spans="2:5">
+    <row r="171" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B171">
         <v>5</v>
       </c>
@@ -4461,7 +4492,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="172" spans="2:5">
+    <row r="172" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B172">
         <v>5</v>
       </c>
@@ -4472,7 +4503,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="173" spans="2:5">
+    <row r="173" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B173">
         <v>5</v>
       </c>
@@ -4483,7 +4514,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="175" spans="2:5">
+    <row r="175" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B175">
         <v>5</v>
       </c>
@@ -4494,7 +4525,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="176" spans="2:5">
+    <row r="176" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B176">
         <v>5</v>
       </c>
@@ -4505,7 +4536,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="177" spans="2:5">
+    <row r="177" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B177">
         <v>5</v>
       </c>
@@ -4516,7 +4547,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="178" spans="2:5">
+    <row r="178" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B178">
         <v>5</v>
       </c>
@@ -4527,7 +4558,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="179" spans="2:5">
+    <row r="179" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B179">
         <v>5</v>
       </c>
@@ -4538,7 +4569,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="180" spans="2:5">
+    <row r="180" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B180">
         <v>5</v>
       </c>
@@ -4549,7 +4580,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="181" spans="2:5">
+    <row r="181" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B181">
         <v>5</v>
       </c>
@@ -4560,7 +4591,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="182" spans="2:5">
+    <row r="182" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B182">
         <v>5</v>
       </c>
@@ -4571,7 +4602,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="184" spans="2:5">
+    <row r="184" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B184">
         <v>5</v>
       </c>
@@ -4582,7 +4613,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="185" spans="2:5">
+    <row r="185" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B185">
         <v>5</v>
       </c>
@@ -4593,7 +4624,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="186" spans="2:5">
+    <row r="186" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B186">
         <v>5</v>
       </c>
@@ -4604,7 +4635,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="187" spans="2:5">
+    <row r="187" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B187">
         <v>5</v>
       </c>
@@ -4615,7 +4646,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="188" spans="2:5">
+    <row r="188" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B188">
         <v>5</v>
       </c>
@@ -4626,7 +4657,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="189" spans="2:5">
+    <row r="189" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B189">
         <v>5</v>
       </c>
@@ -4637,7 +4668,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="190" spans="2:5">
+    <row r="190" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B190">
         <v>5</v>
       </c>
@@ -4648,7 +4679,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="191" spans="2:5">
+    <row r="191" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B191">
         <v>5</v>
       </c>
@@ -4659,7 +4690,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="193" spans="4:5">
+    <row r="193" spans="4:5" x14ac:dyDescent="0.2">
       <c r="D193" s="6"/>
       <c r="E193" s="7"/>
     </row>

--- a/Tasks.xlsx
+++ b/Tasks.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jacopodonati/Documents/PROGETTI/TRAVELMINDER/ai-travel-planner/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/exler/VSCode_Projects/ai-travel-planner/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC8C1117-651F-C448-AF2C-887FE43AEF47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B20BBC4A-8766-3447-B355-51CB2FE6F212}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="33600" windowHeight="18860" xr2:uid="{834F46D4-8CFA-4605-9F2C-653FA769D6F4}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="33600" windowHeight="18860" xr2:uid="{834F46D4-8CFA-4605-9F2C-653FA769D6F4}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="204">
   <si>
     <t>Project Setup</t>
   </si>
@@ -844,7 +844,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -862,7 +862,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="de-DE"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1081,7 +1081,7 @@
                   <c:v>137</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>104</c:v>
+                  <c:v>99</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1984,7 +1984,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -2383,7 +2383,7 @@
         <v>0</v>
       </c>
       <c r="J5">
-        <f>COUNTIF($F$5:$F$199,H5)</f>
+        <f t="shared" ref="J5:J10" si="0">COUNTIF($F$5:$F$199,H5)</f>
         <v>0</v>
       </c>
       <c r="K5">
@@ -2417,7 +2417,7 @@
         <v>33</v>
       </c>
       <c r="J6">
-        <f>COUNTIF($F$5:$F$199,H6)</f>
+        <f t="shared" si="0"/>
         <v>28</v>
       </c>
       <c r="K6">
@@ -2449,24 +2449,24 @@
         <v>2</v>
       </c>
       <c r="I7">
-        <f t="shared" ref="I7:I10" si="0">COUNTIF($B$5:$B$1900,H7)</f>
+        <f t="shared" ref="I7:I10" si="1">COUNTIF($B$5:$B$1900,H7)</f>
         <v>33</v>
       </c>
       <c r="J7">
-        <f>COUNTIF($F$5:$F$199,H7)</f>
-        <v>33</v>
+        <f t="shared" si="0"/>
+        <v>38</v>
       </c>
       <c r="K7">
-        <f t="shared" ref="K7:K10" si="1">K6-I7</f>
+        <f t="shared" ref="K7:K10" si="2">K6-I7</f>
         <v>99</v>
       </c>
       <c r="L7">
-        <f t="shared" ref="L7:L10" si="2">IF(H7&gt;$L$3,"",L6-J7)</f>
-        <v>104</v>
+        <f t="shared" ref="L7:L10" si="3">IF(H7&gt;$L$3,"",L6-J7)</f>
+        <v>99</v>
       </c>
       <c r="M7">
         <f>IF(H7&gt;$L$3,"",L7)</f>
-        <v>104</v>
+        <v>99</v>
       </c>
     </row>
     <row r="8" spans="2:13" x14ac:dyDescent="0.2">
@@ -2489,19 +2489,19 @@
         <v>3</v>
       </c>
       <c r="I8">
+        <f t="shared" si="1"/>
+        <v>33</v>
+      </c>
+      <c r="J8">
         <f t="shared" si="0"/>
-        <v>33</v>
-      </c>
-      <c r="J8">
-        <f>COUNTIF($F$5:$F$199,H8)</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="K8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>66</v>
       </c>
       <c r="L8" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="M8" t="str">
@@ -2529,19 +2529,19 @@
         <v>4</v>
       </c>
       <c r="I9">
+        <f t="shared" si="1"/>
+        <v>38</v>
+      </c>
+      <c r="J9">
         <f t="shared" si="0"/>
-        <v>38</v>
-      </c>
-      <c r="J9">
-        <f>COUNTIF($F$5:$F$199,H9)</f>
         <v>0</v>
       </c>
       <c r="K9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>28</v>
       </c>
       <c r="L9" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="M9" t="str">
@@ -2569,19 +2569,19 @@
         <v>5</v>
       </c>
       <c r="I10">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+      <c r="J10">
         <f t="shared" si="0"/>
-        <v>28</v>
-      </c>
-      <c r="J10">
-        <f>COUNTIF($F$5:$F$199,H10)</f>
         <v>0</v>
       </c>
       <c r="K10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="M10" t="str">
@@ -2983,6 +2983,9 @@
       <c r="E36" s="2" t="s">
         <v>29</v>
       </c>
+      <c r="F36">
+        <v>2</v>
+      </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B37">
@@ -2997,6 +3000,9 @@
       <c r="E37" s="2" t="s">
         <v>30</v>
       </c>
+      <c r="F37">
+        <v>2</v>
+      </c>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38">
@@ -3011,6 +3017,9 @@
       <c r="E38" s="2" t="s">
         <v>31</v>
       </c>
+      <c r="F38">
+        <v>2</v>
+      </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B39">
@@ -3025,6 +3034,9 @@
       <c r="E39" s="2" t="s">
         <v>32</v>
       </c>
+      <c r="F39">
+        <v>2</v>
+      </c>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B40">
@@ -3039,6 +3051,9 @@
       <c r="E40" s="2" t="s">
         <v>33</v>
       </c>
+      <c r="F40">
+        <v>2</v>
+      </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B42">
@@ -3605,16 +3620,25 @@
       <c r="B80">
         <v>3</v>
       </c>
+      <c r="C80" t="s">
+        <v>201</v>
+      </c>
       <c r="D80" s="3" t="s">
         <v>70</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="81" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="F80">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B81">
         <v>3</v>
+      </c>
+      <c r="C81" t="s">
+        <v>201</v>
       </c>
       <c r="D81" s="3" t="s">
         <v>70</v>
@@ -3622,10 +3646,16 @@
       <c r="E81" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="82" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="F81">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B82">
         <v>3</v>
+      </c>
+      <c r="C82" t="s">
+        <v>201</v>
       </c>
       <c r="D82" s="3" t="s">
         <v>70</v>
@@ -3633,10 +3663,16 @@
       <c r="E82" s="2" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="83" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="F82">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="83" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B83">
         <v>3</v>
+      </c>
+      <c r="C83" t="s">
+        <v>201</v>
       </c>
       <c r="D83" s="3" t="s">
         <v>70</v>
@@ -3644,10 +3680,16 @@
       <c r="E83" s="2" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="85" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="F83">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="85" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B85">
         <v>3</v>
+      </c>
+      <c r="C85" t="s">
+        <v>201</v>
       </c>
       <c r="D85" s="3" t="s">
         <v>75</v>
@@ -3655,10 +3697,16 @@
       <c r="E85" s="2" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="86" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="F85">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="86" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B86">
         <v>3</v>
+      </c>
+      <c r="C86" t="s">
+        <v>201</v>
       </c>
       <c r="D86" s="3" t="s">
         <v>75</v>
@@ -3666,10 +3714,16 @@
       <c r="E86" s="2" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="87" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="F86">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="87" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B87">
         <v>3</v>
+      </c>
+      <c r="C87" t="s">
+        <v>201</v>
       </c>
       <c r="D87" s="3" t="s">
         <v>75</v>
@@ -3677,10 +3731,16 @@
       <c r="E87" s="2" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="88" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="F87">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="88" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B88">
         <v>3</v>
+      </c>
+      <c r="C88" t="s">
+        <v>201</v>
       </c>
       <c r="D88" s="3" t="s">
         <v>75</v>
@@ -3688,10 +3748,16 @@
       <c r="E88" s="2" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="89" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="F88">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="89" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B89">
         <v>3</v>
+      </c>
+      <c r="C89" t="s">
+        <v>201</v>
       </c>
       <c r="D89" s="3" t="s">
         <v>75</v>
@@ -3699,10 +3765,16 @@
       <c r="E89" s="2" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="90" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="F89">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B90">
         <v>3</v>
+      </c>
+      <c r="C90" t="s">
+        <v>201</v>
       </c>
       <c r="D90" s="3" t="s">
         <v>75</v>
@@ -3710,10 +3782,16 @@
       <c r="E90" s="2" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="91" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="F90">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="91" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B91">
         <v>3</v>
+      </c>
+      <c r="C91" t="s">
+        <v>201</v>
       </c>
       <c r="D91" s="3" t="s">
         <v>75</v>
@@ -3721,10 +3799,16 @@
       <c r="E91" s="2" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="92" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="F91">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B92">
         <v>3</v>
+      </c>
+      <c r="C92" t="s">
+        <v>201</v>
       </c>
       <c r="D92" s="3" t="s">
         <v>75</v>
@@ -3732,10 +3816,16 @@
       <c r="E92" s="2" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="93" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="F92">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="93" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B93">
         <v>3</v>
+      </c>
+      <c r="C93" t="s">
+        <v>201</v>
       </c>
       <c r="D93" s="3" t="s">
         <v>75</v>
@@ -3743,10 +3833,16 @@
       <c r="E93" s="2" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="94" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="F93">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="94" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B94">
         <v>3</v>
+      </c>
+      <c r="C94" t="s">
+        <v>201</v>
       </c>
       <c r="D94" s="3" t="s">
         <v>75</v>
@@ -3754,16 +3850,25 @@
       <c r="E94" s="2" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="95" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="F94">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B95">
         <v>3</v>
+      </c>
+      <c r="C95" t="s">
+        <v>201</v>
       </c>
       <c r="D95" s="3" t="s">
         <v>75</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>86</v>
+      </c>
+      <c r="F95">
+        <v>3</v>
       </c>
     </row>
     <row r="97" spans="2:5" x14ac:dyDescent="0.2">

--- a/Tasks.xlsx
+++ b/Tasks.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/exler/VSCode_Projects/ai-travel-planner/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pas02\Nextcloud\Documents\03_Data Science - Uni Stuttgart\06_SoS 2026\04_Software Engineering\Group project 3\ai-travel-planner\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B20BBC4A-8766-3447-B355-51CB2FE6F212}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="33600" windowHeight="18860" xr2:uid="{834F46D4-8CFA-4605-9F2C-653FA769D6F4}"/>
+    <workbookView xWindow="2940" yWindow="2940" windowWidth="21600" windowHeight="11295" xr2:uid="{834F46D4-8CFA-4605-9F2C-653FA769D6F4}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -763,7 +763,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2301,16 +2301,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67F1D602-D536-4BC9-865A-CD2C06CAE9C2}">
   <dimension ref="B2:M193"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="6.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-    <col min="4" max="4" width="29.6640625" customWidth="1"/>
-    <col min="5" max="5" width="66.1640625" customWidth="1"/>
-    <col min="6" max="6" width="12.5" customWidth="1"/>
+    <col min="2" max="2" width="6.85546875" customWidth="1"/>
+    <col min="3" max="3" width="22.85546875" customWidth="1"/>
+    <col min="4" max="4" width="29.7109375" customWidth="1"/>
+    <col min="5" max="5" width="66.140625" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:13" ht="22" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:13" ht="21">
       <c r="B2" s="5" t="s">
         <v>191</v>
       </c>
@@ -2319,7 +2319,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:13">
       <c r="E3" s="4"/>
       <c r="K3" t="s">
         <v>199</v>
@@ -2328,7 +2328,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:13">
       <c r="B4" s="1" t="s">
         <v>188</v>
       </c>
@@ -2360,7 +2360,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:13">
       <c r="B5">
         <v>1</v>
       </c>
@@ -2393,7 +2393,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:13">
       <c r="B6">
         <v>1</v>
       </c>
@@ -2429,7 +2429,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="7" spans="2:13" ht="17" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:13">
       <c r="B7">
         <v>1</v>
       </c>
@@ -2469,7 +2469,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:13">
       <c r="B8">
         <v>1</v>
       </c>
@@ -2509,7 +2509,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:13">
       <c r="B9">
         <v>1</v>
       </c>
@@ -2549,7 +2549,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:13">
       <c r="B10">
         <v>1</v>
       </c>
@@ -2589,7 +2589,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:13">
       <c r="B11">
         <v>1</v>
       </c>
@@ -2613,7 +2613,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:13">
       <c r="B12">
         <v>1</v>
       </c>
@@ -2630,7 +2630,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:13">
       <c r="B14">
         <v>1</v>
       </c>
@@ -2647,7 +2647,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:13">
       <c r="B15">
         <v>1</v>
       </c>
@@ -2664,7 +2664,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="2:13" ht="17" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:13">
       <c r="B16">
         <v>1</v>
       </c>
@@ -2681,7 +2681,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="2:6" ht="17" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:6">
       <c r="B17">
         <v>1</v>
       </c>
@@ -2698,7 +2698,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:6">
       <c r="B18">
         <v>1</v>
       </c>
@@ -2715,7 +2715,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:6">
       <c r="B19">
         <v>1</v>
       </c>
@@ -2732,7 +2732,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:6">
       <c r="B20">
         <v>1</v>
       </c>
@@ -2749,7 +2749,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:6">
       <c r="B22">
         <v>1</v>
       </c>
@@ -2766,7 +2766,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:6">
       <c r="B23">
         <v>1</v>
       </c>
@@ -2783,7 +2783,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:6">
       <c r="B24">
         <v>1</v>
       </c>
@@ -2800,7 +2800,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:6">
       <c r="B25">
         <v>1</v>
       </c>
@@ -2817,7 +2817,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:6">
       <c r="B26">
         <v>1</v>
       </c>
@@ -2834,7 +2834,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:6">
       <c r="B27">
         <v>1</v>
       </c>
@@ -2851,7 +2851,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:6">
       <c r="B28">
         <v>1</v>
       </c>
@@ -2868,7 +2868,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:6">
       <c r="B29">
         <v>1</v>
       </c>
@@ -2885,7 +2885,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:6">
       <c r="B30">
         <v>1</v>
       </c>
@@ -2902,7 +2902,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:6">
       <c r="B31">
         <v>1</v>
       </c>
@@ -2919,7 +2919,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:6">
       <c r="B32">
         <v>1</v>
       </c>
@@ -2936,7 +2936,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:6">
       <c r="B33">
         <v>1</v>
       </c>
@@ -2953,7 +2953,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:6">
       <c r="B34">
         <v>1</v>
       </c>
@@ -2970,7 +2970,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:6">
       <c r="B36">
         <v>1</v>
       </c>
@@ -2987,7 +2987,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:6">
       <c r="B37">
         <v>1</v>
       </c>
@@ -3004,7 +3004,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:6">
       <c r="B38">
         <v>1</v>
       </c>
@@ -3021,7 +3021,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:6">
       <c r="B39">
         <v>1</v>
       </c>
@@ -3038,7 +3038,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:6">
       <c r="B40">
         <v>1</v>
       </c>
@@ -3055,7 +3055,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:6">
       <c r="B42">
         <v>2</v>
       </c>
@@ -3072,7 +3072,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="43" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:6">
       <c r="B43">
         <v>2</v>
       </c>
@@ -3089,7 +3089,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="44" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:6">
       <c r="B44">
         <v>2</v>
       </c>
@@ -3106,7 +3106,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="45" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:6">
       <c r="B45">
         <v>2</v>
       </c>
@@ -3123,7 +3123,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="46" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:6">
       <c r="B46">
         <v>2</v>
       </c>
@@ -3140,7 +3140,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="47" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:6">
       <c r="B47">
         <v>2</v>
       </c>
@@ -3157,7 +3157,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="48" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:6">
       <c r="B48">
         <v>2</v>
       </c>
@@ -3174,7 +3174,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="50" spans="2:6">
       <c r="B50">
         <v>2</v>
       </c>
@@ -3191,7 +3191,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="51" spans="2:6">
       <c r="B51">
         <v>2</v>
       </c>
@@ -3208,7 +3208,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="52" spans="2:6">
       <c r="B52">
         <v>2</v>
       </c>
@@ -3225,7 +3225,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="53" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="53" spans="2:6">
       <c r="B53">
         <v>2</v>
       </c>
@@ -3242,7 +3242,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="54" spans="2:6">
       <c r="B54">
         <v>2</v>
       </c>
@@ -3259,7 +3259,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="55" spans="2:6">
       <c r="B55">
         <v>2</v>
       </c>
@@ -3276,7 +3276,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="57" spans="2:6" ht="17" x14ac:dyDescent="0.2">
+    <row r="57" spans="2:6">
       <c r="B57">
         <v>2</v>
       </c>
@@ -3293,7 +3293,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="58" spans="2:6">
       <c r="B58">
         <v>2</v>
       </c>
@@ -3310,7 +3310,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="59" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="59" spans="2:6">
       <c r="B59">
         <v>2</v>
       </c>
@@ -3327,7 +3327,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="60" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="60" spans="2:6">
       <c r="B60">
         <v>2</v>
       </c>
@@ -3344,7 +3344,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="61" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="61" spans="2:6">
       <c r="B61">
         <v>2</v>
       </c>
@@ -3361,7 +3361,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="62" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="62" spans="2:6">
       <c r="B62">
         <v>2</v>
       </c>
@@ -3378,7 +3378,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="64" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="64" spans="2:6">
       <c r="B64">
         <v>2</v>
       </c>
@@ -3395,7 +3395,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="65" spans="2:6" ht="17" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:6">
       <c r="B65">
         <v>2</v>
       </c>
@@ -3412,7 +3412,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="66" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:6">
       <c r="B66">
         <v>2</v>
       </c>
@@ -3429,7 +3429,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="67" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:6">
       <c r="B67">
         <v>2</v>
       </c>
@@ -3446,7 +3446,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="68" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:6">
       <c r="B68">
         <v>2</v>
       </c>
@@ -3463,7 +3463,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="69" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:6">
       <c r="B69">
         <v>2</v>
       </c>
@@ -3480,7 +3480,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="71" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:6">
       <c r="B71">
         <v>2</v>
       </c>
@@ -3497,7 +3497,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="72" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:6">
       <c r="B72">
         <v>2</v>
       </c>
@@ -3514,7 +3514,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="73" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:6">
       <c r="B73">
         <v>2</v>
       </c>
@@ -3531,7 +3531,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="74" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:6">
       <c r="B74">
         <v>2</v>
       </c>
@@ -3548,7 +3548,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="75" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:6">
       <c r="B75">
         <v>2</v>
       </c>
@@ -3565,7 +3565,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="76" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:6">
       <c r="B76">
         <v>2</v>
       </c>
@@ -3582,7 +3582,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="77" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:6">
       <c r="B77">
         <v>2</v>
       </c>
@@ -3599,7 +3599,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="78" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="78" spans="2:6">
       <c r="B78">
         <v>2</v>
       </c>
@@ -3616,7 +3616,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="80" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:6">
       <c r="B80">
         <v>3</v>
       </c>
@@ -3633,7 +3633,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="81" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="81" spans="2:6">
       <c r="B81">
         <v>3</v>
       </c>
@@ -3650,7 +3650,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="82" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="82" spans="2:6">
       <c r="B82">
         <v>3</v>
       </c>
@@ -3667,7 +3667,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="83" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="83" spans="2:6">
       <c r="B83">
         <v>3</v>
       </c>
@@ -3684,7 +3684,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="85" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="85" spans="2:6">
       <c r="B85">
         <v>3</v>
       </c>
@@ -3701,7 +3701,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="86" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="86" spans="2:6">
       <c r="B86">
         <v>3</v>
       </c>
@@ -3718,7 +3718,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="87" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="87" spans="2:6">
       <c r="B87">
         <v>3</v>
       </c>
@@ -3735,7 +3735,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="88" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="88" spans="2:6">
       <c r="B88">
         <v>3</v>
       </c>
@@ -3752,7 +3752,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="89" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="89" spans="2:6">
       <c r="B89">
         <v>3</v>
       </c>
@@ -3769,7 +3769,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="90" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="90" spans="2:6">
       <c r="B90">
         <v>3</v>
       </c>
@@ -3786,7 +3786,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="91" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="91" spans="2:6">
       <c r="B91">
         <v>3</v>
       </c>
@@ -3803,7 +3803,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="92" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="92" spans="2:6">
       <c r="B92">
         <v>3</v>
       </c>
@@ -3820,7 +3820,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="93" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="93" spans="2:6">
       <c r="B93">
         <v>3</v>
       </c>
@@ -3837,7 +3837,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="94" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="94" spans="2:6">
       <c r="B94">
         <v>3</v>
       </c>
@@ -3854,7 +3854,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="95" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="95" spans="2:6">
       <c r="B95">
         <v>3</v>
       </c>
@@ -3871,7 +3871,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="97" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="97" spans="2:5">
       <c r="B97">
         <v>3</v>
       </c>
@@ -3882,7 +3882,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="98" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="98" spans="2:5">
       <c r="B98">
         <v>3</v>
       </c>
@@ -3893,7 +3893,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="99" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="99" spans="2:5">
       <c r="B99">
         <v>3</v>
       </c>
@@ -3904,7 +3904,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="100" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="100" spans="2:5">
       <c r="B100">
         <v>3</v>
       </c>
@@ -3915,7 +3915,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="101" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="101" spans="2:5">
       <c r="B101">
         <v>3</v>
       </c>
@@ -3926,7 +3926,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="102" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="102" spans="2:5">
       <c r="B102">
         <v>3</v>
       </c>
@@ -3937,7 +3937,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="103" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="103" spans="2:5">
       <c r="B103">
         <v>3</v>
       </c>
@@ -3948,7 +3948,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="104" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="104" spans="2:5">
       <c r="B104">
         <v>3</v>
       </c>
@@ -3959,7 +3959,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="105" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="105" spans="2:5">
       <c r="B105">
         <v>3</v>
       </c>
@@ -3970,7 +3970,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="106" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="106" spans="2:5">
       <c r="B106">
         <v>3</v>
       </c>
@@ -3981,7 +3981,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="108" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="108" spans="2:5">
       <c r="B108">
         <v>3</v>
       </c>
@@ -3992,7 +3992,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="109" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="109" spans="2:5">
       <c r="B109">
         <v>3</v>
       </c>
@@ -4003,7 +4003,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="110" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="110" spans="2:5">
       <c r="B110">
         <v>3</v>
       </c>
@@ -4014,7 +4014,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="111" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="111" spans="2:5">
       <c r="B111">
         <v>3</v>
       </c>
@@ -4025,7 +4025,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="112" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="112" spans="2:5">
       <c r="B112">
         <v>3</v>
       </c>
@@ -4036,7 +4036,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="114" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="114" spans="2:5">
       <c r="B114">
         <v>3</v>
       </c>
@@ -4047,7 +4047,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="115" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="115" spans="2:5">
       <c r="B115">
         <v>3</v>
       </c>
@@ -4058,7 +4058,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="116" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="116" spans="2:5">
       <c r="B116">
         <v>3</v>
       </c>
@@ -4069,7 +4069,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="118" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="118" spans="2:5">
       <c r="B118">
         <v>4</v>
       </c>
@@ -4080,7 +4080,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="119" spans="2:5" ht="17" x14ac:dyDescent="0.2">
+    <row r="119" spans="2:5">
       <c r="B119">
         <v>4</v>
       </c>
@@ -4091,7 +4091,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="120" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="120" spans="2:5">
       <c r="B120">
         <v>4</v>
       </c>
@@ -4102,7 +4102,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="121" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="121" spans="2:5">
       <c r="B121">
         <v>4</v>
       </c>
@@ -4113,7 +4113,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="122" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="122" spans="2:5">
       <c r="B122">
         <v>4</v>
       </c>
@@ -4124,7 +4124,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="123" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="123" spans="2:5">
       <c r="B123">
         <v>4</v>
       </c>
@@ -4135,7 +4135,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="125" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="125" spans="2:5">
       <c r="B125">
         <v>4</v>
       </c>
@@ -4146,7 +4146,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="126" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="126" spans="2:5">
       <c r="B126">
         <v>4</v>
       </c>
@@ -4157,7 +4157,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="127" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="127" spans="2:5">
       <c r="B127">
         <v>4</v>
       </c>
@@ -4168,7 +4168,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="128" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="128" spans="2:5">
       <c r="B128">
         <v>4</v>
       </c>
@@ -4179,7 +4179,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="129" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="129" spans="2:5">
       <c r="B129">
         <v>4</v>
       </c>
@@ -4190,7 +4190,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="130" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="130" spans="2:5">
       <c r="B130">
         <v>4</v>
       </c>
@@ -4201,7 +4201,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="131" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="131" spans="2:5">
       <c r="B131">
         <v>4</v>
       </c>
@@ -4212,7 +4212,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="132" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="132" spans="2:5">
       <c r="B132">
         <v>4</v>
       </c>
@@ -4223,7 +4223,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="133" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="133" spans="2:5">
       <c r="B133">
         <v>4</v>
       </c>
@@ -4234,7 +4234,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="134" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="134" spans="2:5">
       <c r="B134">
         <v>4</v>
       </c>
@@ -4245,7 +4245,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="135" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="135" spans="2:5">
       <c r="B135">
         <v>4</v>
       </c>
@@ -4256,7 +4256,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="137" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="137" spans="2:5">
       <c r="B137">
         <v>4</v>
       </c>
@@ -4267,7 +4267,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="138" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="138" spans="2:5">
       <c r="B138">
         <v>4</v>
       </c>
@@ -4278,7 +4278,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="139" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="139" spans="2:5">
       <c r="B139">
         <v>4</v>
       </c>
@@ -4289,7 +4289,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="140" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="140" spans="2:5">
       <c r="B140">
         <v>4</v>
       </c>
@@ -4300,7 +4300,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="142" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="142" spans="2:5">
       <c r="B142">
         <v>4</v>
       </c>
@@ -4311,7 +4311,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="143" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="143" spans="2:5">
       <c r="B143">
         <v>4</v>
       </c>
@@ -4322,7 +4322,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="144" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="144" spans="2:5">
       <c r="B144">
         <v>4</v>
       </c>
@@ -4333,7 +4333,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="145" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="145" spans="2:5">
       <c r="B145">
         <v>4</v>
       </c>
@@ -4344,7 +4344,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="146" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="146" spans="2:5">
       <c r="B146">
         <v>4</v>
       </c>
@@ -4355,7 +4355,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="147" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="147" spans="2:5">
       <c r="B147">
         <v>4</v>
       </c>
@@ -4366,7 +4366,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="148" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="148" spans="2:5">
       <c r="B148">
         <v>4</v>
       </c>
@@ -4377,7 +4377,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="150" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="150" spans="2:5">
       <c r="B150">
         <v>4</v>
       </c>
@@ -4388,7 +4388,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="151" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="151" spans="2:5">
       <c r="B151">
         <v>4</v>
       </c>
@@ -4399,7 +4399,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="152" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="152" spans="2:5">
       <c r="B152">
         <v>4</v>
       </c>
@@ -4410,7 +4410,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="153" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="153" spans="2:5">
       <c r="B153">
         <v>4</v>
       </c>
@@ -4421,7 +4421,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="154" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="154" spans="2:5">
       <c r="B154">
         <v>4</v>
       </c>
@@ -4432,7 +4432,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="155" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="155" spans="2:5">
       <c r="B155">
         <v>4</v>
       </c>
@@ -4443,7 +4443,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="156" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="156" spans="2:5">
       <c r="B156">
         <v>4</v>
       </c>
@@ -4454,7 +4454,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="157" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="157" spans="2:5">
       <c r="B157">
         <v>4</v>
       </c>
@@ -4465,7 +4465,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="158" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="158" spans="2:5">
       <c r="B158">
         <v>4</v>
       </c>
@@ -4476,7 +4476,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="159" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="159" spans="2:5">
       <c r="B159">
         <v>4</v>
       </c>
@@ -4487,7 +4487,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="161" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="161" spans="2:5">
       <c r="B161">
         <v>5</v>
       </c>
@@ -4498,7 +4498,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="162" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="162" spans="2:5">
       <c r="B162">
         <v>5</v>
       </c>
@@ -4509,7 +4509,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="163" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="163" spans="2:5">
       <c r="B163">
         <v>5</v>
       </c>
@@ -4520,7 +4520,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="164" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="164" spans="2:5">
       <c r="B164">
         <v>5</v>
       </c>
@@ -4531,7 +4531,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="165" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="165" spans="2:5">
       <c r="B165">
         <v>5</v>
       </c>
@@ -4542,7 +4542,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="166" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="166" spans="2:5">
       <c r="B166">
         <v>5</v>
       </c>
@@ -4553,7 +4553,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="167" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="167" spans="2:5">
       <c r="B167">
         <v>5</v>
       </c>
@@ -4564,7 +4564,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="169" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="169" spans="2:5">
       <c r="B169">
         <v>5</v>
       </c>
@@ -4575,7 +4575,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="170" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="170" spans="2:5">
       <c r="B170">
         <v>5</v>
       </c>
@@ -4586,7 +4586,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="171" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="171" spans="2:5">
       <c r="B171">
         <v>5</v>
       </c>
@@ -4597,7 +4597,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="172" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="172" spans="2:5">
       <c r="B172">
         <v>5</v>
       </c>
@@ -4608,7 +4608,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="173" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="173" spans="2:5">
       <c r="B173">
         <v>5</v>
       </c>
@@ -4619,7 +4619,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="175" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="175" spans="2:5">
       <c r="B175">
         <v>5</v>
       </c>
@@ -4630,7 +4630,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="176" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="176" spans="2:5">
       <c r="B176">
         <v>5</v>
       </c>
@@ -4641,7 +4641,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="177" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="177" spans="2:5">
       <c r="B177">
         <v>5</v>
       </c>
@@ -4652,7 +4652,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="178" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="178" spans="2:5">
       <c r="B178">
         <v>5</v>
       </c>
@@ -4663,7 +4663,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="179" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="179" spans="2:5">
       <c r="B179">
         <v>5</v>
       </c>
@@ -4674,7 +4674,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="180" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="180" spans="2:5">
       <c r="B180">
         <v>5</v>
       </c>
@@ -4685,7 +4685,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="181" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="181" spans="2:5">
       <c r="B181">
         <v>5</v>
       </c>
@@ -4696,7 +4696,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="182" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="182" spans="2:5">
       <c r="B182">
         <v>5</v>
       </c>
@@ -4707,7 +4707,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="184" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="184" spans="2:5">
       <c r="B184">
         <v>5</v>
       </c>
@@ -4718,7 +4718,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="185" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="185" spans="2:5">
       <c r="B185">
         <v>5</v>
       </c>
@@ -4729,7 +4729,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="186" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="186" spans="2:5">
       <c r="B186">
         <v>5</v>
       </c>
@@ -4740,7 +4740,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="187" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="187" spans="2:5">
       <c r="B187">
         <v>5</v>
       </c>
@@ -4751,7 +4751,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="188" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="188" spans="2:5">
       <c r="B188">
         <v>5</v>
       </c>
@@ -4762,7 +4762,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="189" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="189" spans="2:5">
       <c r="B189">
         <v>5</v>
       </c>
@@ -4773,7 +4773,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="190" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="190" spans="2:5">
       <c r="B190">
         <v>5</v>
       </c>
@@ -4784,7 +4784,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="191" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="191" spans="2:5">
       <c r="B191">
         <v>5</v>
       </c>
@@ -4795,7 +4795,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="193" spans="4:5" x14ac:dyDescent="0.2">
+    <row r="193" spans="4:5">
       <c r="D193" s="6"/>
       <c r="E193" s="7"/>
     </row>

--- a/Tasks.xlsx
+++ b/Tasks.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11130"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pas02\Nextcloud\Documents\03_Data Science - Uni Stuttgart\06_SoS 2026\04_Software Engineering\Group project 3\ai-travel-planner\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jacopodonati/Documents/PROGETTI/TRAVELMINDER/ai-travel-planner/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B20BBC4A-8766-3447-B355-51CB2FE6F212}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6465E58-F374-294C-99D3-0E516C95C3C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2940" yWindow="2940" windowWidth="21600" windowHeight="11295" xr2:uid="{834F46D4-8CFA-4605-9F2C-653FA769D6F4}"/>
+    <workbookView xWindow="2940" yWindow="2940" windowWidth="30440" windowHeight="16320" xr2:uid="{834F46D4-8CFA-4605-9F2C-653FA769D6F4}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="204">
   <si>
     <t>Project Setup</t>
   </si>
@@ -763,7 +763,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -844,7 +844,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -862,7 +862,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="de-DE"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1984,7 +1984,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -2301,16 +2301,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67F1D602-D536-4BC9-865A-CD2C06CAE9C2}">
   <dimension ref="B2:M193"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="6.85546875" customWidth="1"/>
-    <col min="3" max="3" width="22.85546875" customWidth="1"/>
-    <col min="4" max="4" width="29.7109375" customWidth="1"/>
-    <col min="5" max="5" width="66.140625" customWidth="1"/>
-    <col min="6" max="6" width="12.42578125" customWidth="1"/>
+    <col min="2" max="2" width="6.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+    <col min="4" max="4" width="29.6640625" customWidth="1"/>
+    <col min="5" max="5" width="66.1640625" customWidth="1"/>
+    <col min="6" max="6" width="12.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:13" ht="21">
+    <row r="2" spans="2:13" ht="22" x14ac:dyDescent="0.3">
       <c r="B2" s="5" t="s">
         <v>191</v>
       </c>
@@ -2319,7 +2319,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="3" spans="2:13">
+    <row r="3" spans="2:13" x14ac:dyDescent="0.2">
       <c r="E3" s="4"/>
       <c r="K3" t="s">
         <v>199</v>
@@ -2328,7 +2328,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="2:13">
+    <row r="4" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B4" s="1" t="s">
         <v>188</v>
       </c>
@@ -2360,7 +2360,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="5" spans="2:13">
+    <row r="5" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B5">
         <v>1</v>
       </c>
@@ -2393,7 +2393,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="6" spans="2:13">
+    <row r="6" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B6">
         <v>1</v>
       </c>
@@ -2429,7 +2429,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="7" spans="2:13">
+    <row r="7" spans="2:13" ht="17" x14ac:dyDescent="0.2">
       <c r="B7">
         <v>1</v>
       </c>
@@ -2469,7 +2469,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="8" spans="2:13">
+    <row r="8" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B8">
         <v>1</v>
       </c>
@@ -2494,7 +2494,7 @@
       </c>
       <c r="J8">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="K8">
         <f t="shared" si="2"/>
@@ -2509,7 +2509,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="2:13">
+    <row r="9" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B9">
         <v>1</v>
       </c>
@@ -2549,7 +2549,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="2:13">
+    <row r="10" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B10">
         <v>1</v>
       </c>
@@ -2589,7 +2589,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="2:13">
+    <row r="11" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B11">
         <v>1</v>
       </c>
@@ -2613,7 +2613,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="12" spans="2:13">
+    <row r="12" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B12">
         <v>1</v>
       </c>
@@ -2630,7 +2630,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="2:13">
+    <row r="14" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B14">
         <v>1</v>
       </c>
@@ -2647,7 +2647,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="2:13">
+    <row r="15" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B15">
         <v>1</v>
       </c>
@@ -2664,7 +2664,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="2:13">
+    <row r="16" spans="2:13" ht="17" x14ac:dyDescent="0.2">
       <c r="B16">
         <v>1</v>
       </c>
@@ -2681,7 +2681,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="2:6">
+    <row r="17" spans="2:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B17">
         <v>1</v>
       </c>
@@ -2698,7 +2698,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="2:6">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B18">
         <v>1</v>
       </c>
@@ -2715,7 +2715,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="2:6">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B19">
         <v>1</v>
       </c>
@@ -2732,7 +2732,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="2:6">
+    <row r="20" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B20">
         <v>1</v>
       </c>
@@ -2749,7 +2749,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="2:6">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22">
         <v>1</v>
       </c>
@@ -2766,7 +2766,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="2:6">
+    <row r="23" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B23">
         <v>1</v>
       </c>
@@ -2783,7 +2783,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="2:6">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B24">
         <v>1</v>
       </c>
@@ -2800,7 +2800,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="2:6">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B25">
         <v>1</v>
       </c>
@@ -2817,7 +2817,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="2:6">
+    <row r="26" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B26">
         <v>1</v>
       </c>
@@ -2834,7 +2834,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="2:6">
+    <row r="27" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B27">
         <v>1</v>
       </c>
@@ -2851,7 +2851,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="2:6">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B28">
         <v>1</v>
       </c>
@@ -2868,7 +2868,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="2:6">
+    <row r="29" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B29">
         <v>1</v>
       </c>
@@ -2885,7 +2885,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="2:6">
+    <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30">
         <v>1</v>
       </c>
@@ -2902,7 +2902,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="2:6">
+    <row r="31" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B31">
         <v>1</v>
       </c>
@@ -2919,7 +2919,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="2:6">
+    <row r="32" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B32">
         <v>1</v>
       </c>
@@ -2936,7 +2936,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="2:6">
+    <row r="33" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B33">
         <v>1</v>
       </c>
@@ -2953,7 +2953,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="2:6">
+    <row r="34" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B34">
         <v>1</v>
       </c>
@@ -2970,7 +2970,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="2:6">
+    <row r="36" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B36">
         <v>1</v>
       </c>
@@ -2987,7 +2987,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="2:6">
+    <row r="37" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B37">
         <v>1</v>
       </c>
@@ -3004,7 +3004,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="2:6">
+    <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38">
         <v>1</v>
       </c>
@@ -3021,7 +3021,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="2:6">
+    <row r="39" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B39">
         <v>1</v>
       </c>
@@ -3038,7 +3038,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="2:6">
+    <row r="40" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B40">
         <v>1</v>
       </c>
@@ -3055,7 +3055,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="2:6">
+    <row r="42" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B42">
         <v>2</v>
       </c>
@@ -3072,7 +3072,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="43" spans="2:6">
+    <row r="43" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B43">
         <v>2</v>
       </c>
@@ -3089,7 +3089,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="44" spans="2:6">
+    <row r="44" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B44">
         <v>2</v>
       </c>
@@ -3106,7 +3106,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="45" spans="2:6">
+    <row r="45" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B45">
         <v>2</v>
       </c>
@@ -3123,7 +3123,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="46" spans="2:6">
+    <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46">
         <v>2</v>
       </c>
@@ -3140,7 +3140,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="47" spans="2:6">
+    <row r="47" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B47">
         <v>2</v>
       </c>
@@ -3157,7 +3157,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="48" spans="2:6">
+    <row r="48" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B48">
         <v>2</v>
       </c>
@@ -3174,7 +3174,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="2:6">
+    <row r="50" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B50">
         <v>2</v>
       </c>
@@ -3191,7 +3191,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="51" spans="2:6">
+    <row r="51" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B51">
         <v>2</v>
       </c>
@@ -3208,7 +3208,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="52" spans="2:6">
+    <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52">
         <v>2</v>
       </c>
@@ -3225,7 +3225,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="53" spans="2:6">
+    <row r="53" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B53">
         <v>2</v>
       </c>
@@ -3242,7 +3242,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="2:6">
+    <row r="54" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B54">
         <v>2</v>
       </c>
@@ -3259,7 +3259,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="55" spans="2:6">
+    <row r="55" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B55">
         <v>2</v>
       </c>
@@ -3276,7 +3276,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="57" spans="2:6">
+    <row r="57" spans="2:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B57">
         <v>2</v>
       </c>
@@ -3293,7 +3293,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="58" spans="2:6">
+    <row r="58" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B58">
         <v>2</v>
       </c>
@@ -3310,7 +3310,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="59" spans="2:6">
+    <row r="59" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B59">
         <v>2</v>
       </c>
@@ -3327,7 +3327,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="60" spans="2:6">
+    <row r="60" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B60">
         <v>2</v>
       </c>
@@ -3344,7 +3344,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="61" spans="2:6">
+    <row r="61" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B61">
         <v>2</v>
       </c>
@@ -3361,7 +3361,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="62" spans="2:6">
+    <row r="62" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B62">
         <v>2</v>
       </c>
@@ -3378,7 +3378,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="64" spans="2:6">
+    <row r="64" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B64">
         <v>2</v>
       </c>
@@ -3395,7 +3395,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="65" spans="2:6">
+    <row r="65" spans="2:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B65">
         <v>2</v>
       </c>
@@ -3412,7 +3412,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="66" spans="2:6">
+    <row r="66" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B66">
         <v>2</v>
       </c>
@@ -3429,7 +3429,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="67" spans="2:6">
+    <row r="67" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B67">
         <v>2</v>
       </c>
@@ -3446,7 +3446,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="68" spans="2:6">
+    <row r="68" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B68">
         <v>2</v>
       </c>
@@ -3463,7 +3463,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="69" spans="2:6">
+    <row r="69" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B69">
         <v>2</v>
       </c>
@@ -3480,7 +3480,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="71" spans="2:6">
+    <row r="71" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B71">
         <v>2</v>
       </c>
@@ -3497,7 +3497,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="72" spans="2:6">
+    <row r="72" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B72">
         <v>2</v>
       </c>
@@ -3514,7 +3514,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="73" spans="2:6">
+    <row r="73" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B73">
         <v>2</v>
       </c>
@@ -3531,7 +3531,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="74" spans="2:6">
+    <row r="74" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B74">
         <v>2</v>
       </c>
@@ -3548,7 +3548,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="75" spans="2:6">
+    <row r="75" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B75">
         <v>2</v>
       </c>
@@ -3565,7 +3565,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="76" spans="2:6">
+    <row r="76" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B76">
         <v>2</v>
       </c>
@@ -3582,7 +3582,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="77" spans="2:6">
+    <row r="77" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B77">
         <v>2</v>
       </c>
@@ -3599,7 +3599,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="78" spans="2:6">
+    <row r="78" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B78">
         <v>2</v>
       </c>
@@ -3616,7 +3616,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="80" spans="2:6">
+    <row r="80" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B80">
         <v>3</v>
       </c>
@@ -3633,7 +3633,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="81" spans="2:6">
+    <row r="81" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B81">
         <v>3</v>
       </c>
@@ -3650,7 +3650,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="82" spans="2:6">
+    <row r="82" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B82">
         <v>3</v>
       </c>
@@ -3667,7 +3667,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="83" spans="2:6">
+    <row r="83" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B83">
         <v>3</v>
       </c>
@@ -3684,7 +3684,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="85" spans="2:6">
+    <row r="85" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B85">
         <v>3</v>
       </c>
@@ -3701,7 +3701,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="86" spans="2:6">
+    <row r="86" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B86">
         <v>3</v>
       </c>
@@ -3718,7 +3718,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="87" spans="2:6">
+    <row r="87" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B87">
         <v>3</v>
       </c>
@@ -3735,7 +3735,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="88" spans="2:6">
+    <row r="88" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B88">
         <v>3</v>
       </c>
@@ -3752,7 +3752,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="89" spans="2:6">
+    <row r="89" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B89">
         <v>3</v>
       </c>
@@ -3769,7 +3769,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="90" spans="2:6">
+    <row r="90" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B90">
         <v>3</v>
       </c>
@@ -3786,7 +3786,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="91" spans="2:6">
+    <row r="91" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B91">
         <v>3</v>
       </c>
@@ -3803,7 +3803,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="92" spans="2:6">
+    <row r="92" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B92">
         <v>3</v>
       </c>
@@ -3820,7 +3820,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="93" spans="2:6">
+    <row r="93" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B93">
         <v>3</v>
       </c>
@@ -3837,7 +3837,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="94" spans="2:6">
+    <row r="94" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B94">
         <v>3</v>
       </c>
@@ -3854,7 +3854,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="95" spans="2:6">
+    <row r="95" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B95">
         <v>3</v>
       </c>
@@ -3871,9 +3871,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="97" spans="2:5">
+    <row r="97" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B97">
         <v>3</v>
+      </c>
+      <c r="C97" t="s">
+        <v>203</v>
       </c>
       <c r="D97" s="3" t="s">
         <v>87</v>
@@ -3881,10 +3884,16 @@
       <c r="E97" s="2" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="98" spans="2:5">
+      <c r="F97">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="98" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B98">
         <v>3</v>
+      </c>
+      <c r="C98" t="s">
+        <v>203</v>
       </c>
       <c r="D98" s="3" t="s">
         <v>87</v>
@@ -3892,10 +3901,16 @@
       <c r="E98" s="2" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="99" spans="2:5">
+      <c r="F98">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="99" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B99">
         <v>3</v>
+      </c>
+      <c r="C99" t="s">
+        <v>203</v>
       </c>
       <c r="D99" s="3" t="s">
         <v>87</v>
@@ -3903,10 +3918,16 @@
       <c r="E99" s="2" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="100" spans="2:5">
+      <c r="F99">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="100" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B100">
         <v>3</v>
+      </c>
+      <c r="C100" t="s">
+        <v>203</v>
       </c>
       <c r="D100" s="3" t="s">
         <v>87</v>
@@ -3914,10 +3935,16 @@
       <c r="E100" s="2" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="101" spans="2:5">
+      <c r="F100">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B101">
         <v>3</v>
+      </c>
+      <c r="C101" t="s">
+        <v>203</v>
       </c>
       <c r="D101" s="3" t="s">
         <v>87</v>
@@ -3925,10 +3952,16 @@
       <c r="E101" s="2" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="102" spans="2:5">
+      <c r="F101">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B102">
         <v>3</v>
+      </c>
+      <c r="C102" t="s">
+        <v>203</v>
       </c>
       <c r="D102" s="3" t="s">
         <v>87</v>
@@ -3936,10 +3969,16 @@
       <c r="E102" s="2" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="103" spans="2:5">
+      <c r="F102">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="103" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B103">
         <v>3</v>
+      </c>
+      <c r="C103" t="s">
+        <v>203</v>
       </c>
       <c r="D103" s="3" t="s">
         <v>87</v>
@@ -3947,10 +3986,16 @@
       <c r="E103" s="2" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="104" spans="2:5">
+      <c r="F103">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="104" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B104">
         <v>3</v>
+      </c>
+      <c r="C104" t="s">
+        <v>203</v>
       </c>
       <c r="D104" s="3" t="s">
         <v>87</v>
@@ -3958,10 +4003,16 @@
       <c r="E104" s="2" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="105" spans="2:5">
+      <c r="F104">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="105" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B105">
         <v>3</v>
+      </c>
+      <c r="C105" t="s">
+        <v>203</v>
       </c>
       <c r="D105" s="3" t="s">
         <v>87</v>
@@ -3969,10 +4020,16 @@
       <c r="E105" s="2" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="106" spans="2:5">
+      <c r="F105">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="106" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B106">
         <v>3</v>
+      </c>
+      <c r="C106" t="s">
+        <v>203</v>
       </c>
       <c r="D106" s="3" t="s">
         <v>87</v>
@@ -3980,10 +4037,16 @@
       <c r="E106" s="2" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="108" spans="2:5">
+      <c r="F106">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="108" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B108">
         <v>3</v>
+      </c>
+      <c r="C108" t="s">
+        <v>203</v>
       </c>
       <c r="D108" s="3" t="s">
         <v>98</v>
@@ -3991,10 +4054,16 @@
       <c r="E108" s="2" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="109" spans="2:5">
+      <c r="F108">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="109" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B109">
         <v>3</v>
+      </c>
+      <c r="C109" t="s">
+        <v>203</v>
       </c>
       <c r="D109" s="3" t="s">
         <v>98</v>
@@ -4002,10 +4071,16 @@
       <c r="E109" s="2" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="110" spans="2:5">
+      <c r="F109">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="110" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B110">
         <v>3</v>
+      </c>
+      <c r="C110" t="s">
+        <v>203</v>
       </c>
       <c r="D110" s="3" t="s">
         <v>98</v>
@@ -4013,10 +4088,16 @@
       <c r="E110" s="2" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="111" spans="2:5">
+      <c r="F110">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="111" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B111">
         <v>3</v>
+      </c>
+      <c r="C111" t="s">
+        <v>203</v>
       </c>
       <c r="D111" s="3" t="s">
         <v>98</v>
@@ -4024,10 +4105,16 @@
       <c r="E111" s="2" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="112" spans="2:5">
+      <c r="F111">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="112" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B112">
         <v>3</v>
+      </c>
+      <c r="C112" t="s">
+        <v>203</v>
       </c>
       <c r="D112" s="3" t="s">
         <v>98</v>
@@ -4035,10 +4122,16 @@
       <c r="E112" s="2" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="114" spans="2:5">
+      <c r="F112">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="114" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B114">
         <v>3</v>
+      </c>
+      <c r="C114" t="s">
+        <v>203</v>
       </c>
       <c r="D114" s="3" t="s">
         <v>104</v>
@@ -4046,10 +4139,16 @@
       <c r="E114" s="2" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="115" spans="2:5">
+      <c r="F114">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="115" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B115">
         <v>3</v>
+      </c>
+      <c r="C115" t="s">
+        <v>203</v>
       </c>
       <c r="D115" s="3" t="s">
         <v>104</v>
@@ -4057,10 +4156,16 @@
       <c r="E115" s="2" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="116" spans="2:5">
+      <c r="F115">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="116" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B116">
         <v>3</v>
+      </c>
+      <c r="C116" t="s">
+        <v>203</v>
       </c>
       <c r="D116" s="3" t="s">
         <v>104</v>
@@ -4068,8 +4173,11 @@
       <c r="E116" s="2" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="118" spans="2:5">
+      <c r="F116">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="118" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B118">
         <v>4</v>
       </c>
@@ -4080,7 +4188,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="119" spans="2:5">
+    <row r="119" spans="2:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B119">
         <v>4</v>
       </c>
@@ -4091,7 +4199,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="120" spans="2:5">
+    <row r="120" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B120">
         <v>4</v>
       </c>
@@ -4102,7 +4210,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="121" spans="2:5">
+    <row r="121" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B121">
         <v>4</v>
       </c>
@@ -4113,7 +4221,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="122" spans="2:5">
+    <row r="122" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B122">
         <v>4</v>
       </c>
@@ -4124,7 +4232,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="123" spans="2:5">
+    <row r="123" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B123">
         <v>4</v>
       </c>
@@ -4135,7 +4243,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="125" spans="2:5">
+    <row r="125" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B125">
         <v>4</v>
       </c>
@@ -4146,7 +4254,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="126" spans="2:5">
+    <row r="126" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B126">
         <v>4</v>
       </c>
@@ -4157,7 +4265,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="127" spans="2:5">
+    <row r="127" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B127">
         <v>4</v>
       </c>
@@ -4168,7 +4276,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="128" spans="2:5">
+    <row r="128" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B128">
         <v>4</v>
       </c>
@@ -4179,7 +4287,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="129" spans="2:5">
+    <row r="129" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B129">
         <v>4</v>
       </c>
@@ -4190,7 +4298,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="130" spans="2:5">
+    <row r="130" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B130">
         <v>4</v>
       </c>
@@ -4201,7 +4309,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="131" spans="2:5">
+    <row r="131" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B131">
         <v>4</v>
       </c>
@@ -4212,7 +4320,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="132" spans="2:5">
+    <row r="132" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B132">
         <v>4</v>
       </c>
@@ -4223,7 +4331,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="133" spans="2:5">
+    <row r="133" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B133">
         <v>4</v>
       </c>
@@ -4234,7 +4342,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="134" spans="2:5">
+    <row r="134" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B134">
         <v>4</v>
       </c>
@@ -4245,7 +4353,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="135" spans="2:5">
+    <row r="135" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B135">
         <v>4</v>
       </c>
@@ -4256,7 +4364,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="137" spans="2:5">
+    <row r="137" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B137">
         <v>4</v>
       </c>
@@ -4267,7 +4375,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="138" spans="2:5">
+    <row r="138" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B138">
         <v>4</v>
       </c>
@@ -4278,7 +4386,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="139" spans="2:5">
+    <row r="139" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B139">
         <v>4</v>
       </c>
@@ -4289,7 +4397,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="140" spans="2:5">
+    <row r="140" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B140">
         <v>4</v>
       </c>
@@ -4300,7 +4408,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="142" spans="2:5">
+    <row r="142" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B142">
         <v>4</v>
       </c>
@@ -4311,7 +4419,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="143" spans="2:5">
+    <row r="143" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B143">
         <v>4</v>
       </c>
@@ -4322,7 +4430,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="144" spans="2:5">
+    <row r="144" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B144">
         <v>4</v>
       </c>
@@ -4333,7 +4441,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="145" spans="2:5">
+    <row r="145" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B145">
         <v>4</v>
       </c>
@@ -4344,7 +4452,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="146" spans="2:5">
+    <row r="146" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B146">
         <v>4</v>
       </c>
@@ -4355,7 +4463,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="147" spans="2:5">
+    <row r="147" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B147">
         <v>4</v>
       </c>
@@ -4366,7 +4474,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="148" spans="2:5">
+    <row r="148" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B148">
         <v>4</v>
       </c>
@@ -4377,7 +4485,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="150" spans="2:5">
+    <row r="150" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B150">
         <v>4</v>
       </c>
@@ -4388,7 +4496,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="151" spans="2:5">
+    <row r="151" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B151">
         <v>4</v>
       </c>
@@ -4399,7 +4507,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="152" spans="2:5">
+    <row r="152" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B152">
         <v>4</v>
       </c>
@@ -4410,7 +4518,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="153" spans="2:5">
+    <row r="153" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B153">
         <v>4</v>
       </c>
@@ -4421,7 +4529,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="154" spans="2:5">
+    <row r="154" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B154">
         <v>4</v>
       </c>
@@ -4432,7 +4540,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="155" spans="2:5">
+    <row r="155" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B155">
         <v>4</v>
       </c>
@@ -4443,7 +4551,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="156" spans="2:5">
+    <row r="156" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B156">
         <v>4</v>
       </c>
@@ -4454,7 +4562,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="157" spans="2:5">
+    <row r="157" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B157">
         <v>4</v>
       </c>
@@ -4465,7 +4573,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="158" spans="2:5">
+    <row r="158" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B158">
         <v>4</v>
       </c>
@@ -4476,7 +4584,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="159" spans="2:5">
+    <row r="159" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B159">
         <v>4</v>
       </c>
@@ -4487,7 +4595,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="161" spans="2:5">
+    <row r="161" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B161">
         <v>5</v>
       </c>
@@ -4498,7 +4606,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="162" spans="2:5">
+    <row r="162" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B162">
         <v>5</v>
       </c>
@@ -4509,7 +4617,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="163" spans="2:5">
+    <row r="163" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B163">
         <v>5</v>
       </c>
@@ -4520,7 +4628,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="164" spans="2:5">
+    <row r="164" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B164">
         <v>5</v>
       </c>
@@ -4531,7 +4639,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="165" spans="2:5">
+    <row r="165" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B165">
         <v>5</v>
       </c>
@@ -4542,7 +4650,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="166" spans="2:5">
+    <row r="166" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B166">
         <v>5</v>
       </c>
@@ -4553,7 +4661,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="167" spans="2:5">
+    <row r="167" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B167">
         <v>5</v>
       </c>
@@ -4564,7 +4672,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="169" spans="2:5">
+    <row r="169" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B169">
         <v>5</v>
       </c>
@@ -4575,7 +4683,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="170" spans="2:5">
+    <row r="170" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B170">
         <v>5</v>
       </c>
@@ -4586,7 +4694,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="171" spans="2:5">
+    <row r="171" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B171">
         <v>5</v>
       </c>
@@ -4597,7 +4705,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="172" spans="2:5">
+    <row r="172" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B172">
         <v>5</v>
       </c>
@@ -4608,7 +4716,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="173" spans="2:5">
+    <row r="173" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B173">
         <v>5</v>
       </c>
@@ -4619,7 +4727,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="175" spans="2:5">
+    <row r="175" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B175">
         <v>5</v>
       </c>
@@ -4630,7 +4738,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="176" spans="2:5">
+    <row r="176" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B176">
         <v>5</v>
       </c>
@@ -4641,7 +4749,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="177" spans="2:5">
+    <row r="177" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B177">
         <v>5</v>
       </c>
@@ -4652,7 +4760,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="178" spans="2:5">
+    <row r="178" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B178">
         <v>5</v>
       </c>
@@ -4663,7 +4771,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="179" spans="2:5">
+    <row r="179" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B179">
         <v>5</v>
       </c>
@@ -4674,7 +4782,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="180" spans="2:5">
+    <row r="180" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B180">
         <v>5</v>
       </c>
@@ -4685,7 +4793,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="181" spans="2:5">
+    <row r="181" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B181">
         <v>5</v>
       </c>
@@ -4696,7 +4804,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="182" spans="2:5">
+    <row r="182" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B182">
         <v>5</v>
       </c>
@@ -4707,7 +4815,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="184" spans="2:5">
+    <row r="184" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B184">
         <v>5</v>
       </c>
@@ -4718,7 +4826,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="185" spans="2:5">
+    <row r="185" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B185">
         <v>5</v>
       </c>
@@ -4729,7 +4837,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="186" spans="2:5">
+    <row r="186" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B186">
         <v>5</v>
       </c>
@@ -4740,7 +4848,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="187" spans="2:5">
+    <row r="187" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B187">
         <v>5</v>
       </c>
@@ -4751,7 +4859,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="188" spans="2:5">
+    <row r="188" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B188">
         <v>5</v>
       </c>
@@ -4762,7 +4870,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="189" spans="2:5">
+    <row r="189" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B189">
         <v>5</v>
       </c>
@@ -4773,7 +4881,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="190" spans="2:5">
+    <row r="190" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B190">
         <v>5</v>
       </c>
@@ -4784,7 +4892,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="191" spans="2:5">
+    <row r="191" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B191">
         <v>5</v>
       </c>
@@ -4795,7 +4903,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="193" spans="4:5">
+    <row r="193" spans="4:5" x14ac:dyDescent="0.2">
       <c r="D193" s="6"/>
       <c r="E193" s="7"/>
     </row>

--- a/Tasks.xlsx
+++ b/Tasks.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jacopodonati/Documents/PROGETTI/TRAVELMINDER/ai-travel-planner/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pas02\Nextcloud\Documents\03_Data Science - Uni Stuttgart\06_SoS 2026\04_Software Engineering\Group project 3\ai-travel-planner\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6465E58-F374-294C-99D3-0E516C95C3C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2940" yWindow="2940" windowWidth="30440" windowHeight="16320" xr2:uid="{834F46D4-8CFA-4605-9F2C-653FA769D6F4}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{834F46D4-8CFA-4605-9F2C-653FA769D6F4}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -763,7 +763,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -844,7 +844,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -862,7 +862,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="de-DE"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1984,7 +1984,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -2301,16 +2301,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67F1D602-D536-4BC9-865A-CD2C06CAE9C2}">
   <dimension ref="B2:M193"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="6.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-    <col min="4" max="4" width="29.6640625" customWidth="1"/>
-    <col min="5" max="5" width="66.1640625" customWidth="1"/>
-    <col min="6" max="6" width="12.5" customWidth="1"/>
+    <col min="2" max="2" width="6.85546875" customWidth="1"/>
+    <col min="3" max="3" width="22.85546875" customWidth="1"/>
+    <col min="4" max="4" width="29.7109375" customWidth="1"/>
+    <col min="5" max="5" width="66.140625" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:13" ht="22" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:13" ht="21">
       <c r="B2" s="5" t="s">
         <v>191</v>
       </c>
@@ -2319,7 +2319,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:13">
       <c r="E3" s="4"/>
       <c r="K3" t="s">
         <v>199</v>
@@ -2328,7 +2328,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:13">
       <c r="B4" s="1" t="s">
         <v>188</v>
       </c>
@@ -2360,7 +2360,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:13">
       <c r="B5">
         <v>1</v>
       </c>
@@ -2393,7 +2393,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:13">
       <c r="B6">
         <v>1</v>
       </c>
@@ -2429,7 +2429,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="7" spans="2:13" ht="17" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:13">
       <c r="B7">
         <v>1</v>
       </c>
@@ -2469,7 +2469,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:13">
       <c r="B8">
         <v>1</v>
       </c>
@@ -2509,7 +2509,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:13">
       <c r="B9">
         <v>1</v>
       </c>
@@ -2549,7 +2549,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:13">
       <c r="B10">
         <v>1</v>
       </c>
@@ -2589,7 +2589,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:13">
       <c r="B11">
         <v>1</v>
       </c>
@@ -2613,7 +2613,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:13">
       <c r="B12">
         <v>1</v>
       </c>
@@ -2630,7 +2630,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:13">
       <c r="B14">
         <v>1</v>
       </c>
@@ -2647,7 +2647,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:13">
       <c r="B15">
         <v>1</v>
       </c>
@@ -2664,7 +2664,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="2:13" ht="17" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:13">
       <c r="B16">
         <v>1</v>
       </c>
@@ -2681,7 +2681,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="2:6" ht="17" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:6">
       <c r="B17">
         <v>1</v>
       </c>
@@ -2698,7 +2698,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:6">
       <c r="B18">
         <v>1</v>
       </c>
@@ -2715,7 +2715,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:6">
       <c r="B19">
         <v>1</v>
       </c>
@@ -2732,7 +2732,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:6">
       <c r="B20">
         <v>1</v>
       </c>
@@ -2749,7 +2749,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:6">
       <c r="B22">
         <v>1</v>
       </c>
@@ -2766,7 +2766,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:6">
       <c r="B23">
         <v>1</v>
       </c>
@@ -2783,7 +2783,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:6">
       <c r="B24">
         <v>1</v>
       </c>
@@ -2800,7 +2800,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:6">
       <c r="B25">
         <v>1</v>
       </c>
@@ -2817,7 +2817,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:6">
       <c r="B26">
         <v>1</v>
       </c>
@@ -2834,7 +2834,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:6">
       <c r="B27">
         <v>1</v>
       </c>
@@ -2851,7 +2851,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:6">
       <c r="B28">
         <v>1</v>
       </c>
@@ -2868,7 +2868,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:6">
       <c r="B29">
         <v>1</v>
       </c>
@@ -2885,7 +2885,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:6">
       <c r="B30">
         <v>1</v>
       </c>
@@ -2902,7 +2902,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:6">
       <c r="B31">
         <v>1</v>
       </c>
@@ -2919,7 +2919,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:6">
       <c r="B32">
         <v>1</v>
       </c>
@@ -2936,7 +2936,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:6">
       <c r="B33">
         <v>1</v>
       </c>
@@ -2953,7 +2953,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:6">
       <c r="B34">
         <v>1</v>
       </c>
@@ -2970,7 +2970,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:6">
       <c r="B36">
         <v>1</v>
       </c>
@@ -2987,7 +2987,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:6">
       <c r="B37">
         <v>1</v>
       </c>
@@ -3004,7 +3004,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:6">
       <c r="B38">
         <v>1</v>
       </c>
@@ -3021,7 +3021,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:6">
       <c r="B39">
         <v>1</v>
       </c>
@@ -3038,7 +3038,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:6">
       <c r="B40">
         <v>1</v>
       </c>
@@ -3055,7 +3055,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:6">
       <c r="B42">
         <v>2</v>
       </c>
@@ -3072,7 +3072,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="43" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:6">
       <c r="B43">
         <v>2</v>
       </c>
@@ -3089,7 +3089,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="44" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:6">
       <c r="B44">
         <v>2</v>
       </c>
@@ -3106,7 +3106,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="45" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:6">
       <c r="B45">
         <v>2</v>
       </c>
@@ -3123,7 +3123,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="46" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:6">
       <c r="B46">
         <v>2</v>
       </c>
@@ -3140,7 +3140,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="47" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:6">
       <c r="B47">
         <v>2</v>
       </c>
@@ -3157,7 +3157,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="48" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:6">
       <c r="B48">
         <v>2</v>
       </c>
@@ -3174,7 +3174,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="50" spans="2:6">
       <c r="B50">
         <v>2</v>
       </c>
@@ -3191,7 +3191,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="51" spans="2:6">
       <c r="B51">
         <v>2</v>
       </c>
@@ -3208,7 +3208,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="52" spans="2:6">
       <c r="B52">
         <v>2</v>
       </c>
@@ -3225,7 +3225,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="53" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="53" spans="2:6">
       <c r="B53">
         <v>2</v>
       </c>
@@ -3242,7 +3242,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="54" spans="2:6">
       <c r="B54">
         <v>2</v>
       </c>
@@ -3259,7 +3259,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="55" spans="2:6">
       <c r="B55">
         <v>2</v>
       </c>
@@ -3276,7 +3276,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="57" spans="2:6" ht="17" x14ac:dyDescent="0.2">
+    <row r="57" spans="2:6">
       <c r="B57">
         <v>2</v>
       </c>
@@ -3293,7 +3293,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="58" spans="2:6">
       <c r="B58">
         <v>2</v>
       </c>
@@ -3310,7 +3310,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="59" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="59" spans="2:6">
       <c r="B59">
         <v>2</v>
       </c>
@@ -3327,7 +3327,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="60" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="60" spans="2:6">
       <c r="B60">
         <v>2</v>
       </c>
@@ -3344,7 +3344,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="61" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="61" spans="2:6">
       <c r="B61">
         <v>2</v>
       </c>
@@ -3361,7 +3361,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="62" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="62" spans="2:6">
       <c r="B62">
         <v>2</v>
       </c>
@@ -3378,7 +3378,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="64" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="64" spans="2:6">
       <c r="B64">
         <v>2</v>
       </c>
@@ -3395,7 +3395,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="65" spans="2:6" ht="17" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:6">
       <c r="B65">
         <v>2</v>
       </c>
@@ -3412,7 +3412,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="66" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:6">
       <c r="B66">
         <v>2</v>
       </c>
@@ -3429,7 +3429,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="67" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:6">
       <c r="B67">
         <v>2</v>
       </c>
@@ -3446,7 +3446,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="68" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:6">
       <c r="B68">
         <v>2</v>
       </c>
@@ -3463,7 +3463,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="69" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:6">
       <c r="B69">
         <v>2</v>
       </c>
@@ -3480,7 +3480,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="71" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:6">
       <c r="B71">
         <v>2</v>
       </c>
@@ -3497,7 +3497,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="72" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:6">
       <c r="B72">
         <v>2</v>
       </c>
@@ -3514,7 +3514,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="73" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:6">
       <c r="B73">
         <v>2</v>
       </c>
@@ -3531,7 +3531,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="74" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:6">
       <c r="B74">
         <v>2</v>
       </c>
@@ -3548,7 +3548,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="75" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:6">
       <c r="B75">
         <v>2</v>
       </c>
@@ -3565,7 +3565,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="76" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:6">
       <c r="B76">
         <v>2</v>
       </c>
@@ -3582,7 +3582,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="77" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:6">
       <c r="B77">
         <v>2</v>
       </c>
@@ -3599,7 +3599,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="78" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="78" spans="2:6">
       <c r="B78">
         <v>2</v>
       </c>
@@ -3616,7 +3616,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="80" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:6">
       <c r="B80">
         <v>3</v>
       </c>
@@ -3633,7 +3633,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="81" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="81" spans="2:6">
       <c r="B81">
         <v>3</v>
       </c>
@@ -3650,7 +3650,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="82" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="82" spans="2:6">
       <c r="B82">
         <v>3</v>
       </c>
@@ -3667,7 +3667,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="83" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="83" spans="2:6">
       <c r="B83">
         <v>3</v>
       </c>
@@ -3684,7 +3684,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="85" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="85" spans="2:6">
       <c r="B85">
         <v>3</v>
       </c>
@@ -3701,7 +3701,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="86" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="86" spans="2:6">
       <c r="B86">
         <v>3</v>
       </c>
@@ -3718,7 +3718,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="87" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="87" spans="2:6">
       <c r="B87">
         <v>3</v>
       </c>
@@ -3735,7 +3735,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="88" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="88" spans="2:6">
       <c r="B88">
         <v>3</v>
       </c>
@@ -3752,7 +3752,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="89" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="89" spans="2:6">
       <c r="B89">
         <v>3</v>
       </c>
@@ -3769,7 +3769,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="90" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="90" spans="2:6">
       <c r="B90">
         <v>3</v>
       </c>
@@ -3786,7 +3786,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="91" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="91" spans="2:6">
       <c r="B91">
         <v>3</v>
       </c>
@@ -3803,7 +3803,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="92" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="92" spans="2:6">
       <c r="B92">
         <v>3</v>
       </c>
@@ -3820,7 +3820,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="93" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="93" spans="2:6">
       <c r="B93">
         <v>3</v>
       </c>
@@ -3837,7 +3837,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="94" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="94" spans="2:6">
       <c r="B94">
         <v>3</v>
       </c>
@@ -3854,7 +3854,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="95" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="95" spans="2:6">
       <c r="B95">
         <v>3</v>
       </c>
@@ -3871,7 +3871,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="97" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="97" spans="2:6">
       <c r="B97">
         <v>3</v>
       </c>
@@ -3888,7 +3888,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="98" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="98" spans="2:6">
       <c r="B98">
         <v>3</v>
       </c>
@@ -3905,7 +3905,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="99" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="99" spans="2:6">
       <c r="B99">
         <v>3</v>
       </c>
@@ -3922,7 +3922,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="100" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="100" spans="2:6">
       <c r="B100">
         <v>3</v>
       </c>
@@ -3939,7 +3939,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="101" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="101" spans="2:6">
       <c r="B101">
         <v>3</v>
       </c>
@@ -3956,7 +3956,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="102" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="102" spans="2:6">
       <c r="B102">
         <v>3</v>
       </c>
@@ -3973,7 +3973,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="103" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="103" spans="2:6">
       <c r="B103">
         <v>3</v>
       </c>
@@ -3990,7 +3990,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="104" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="104" spans="2:6">
       <c r="B104">
         <v>3</v>
       </c>
@@ -4007,7 +4007,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="105" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="105" spans="2:6">
       <c r="B105">
         <v>3</v>
       </c>
@@ -4024,7 +4024,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="106" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="106" spans="2:6">
       <c r="B106">
         <v>3</v>
       </c>
@@ -4041,7 +4041,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="108" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="108" spans="2:6">
       <c r="B108">
         <v>3</v>
       </c>
@@ -4058,7 +4058,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="109" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="109" spans="2:6">
       <c r="B109">
         <v>3</v>
       </c>
@@ -4075,7 +4075,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="110" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="110" spans="2:6">
       <c r="B110">
         <v>3</v>
       </c>
@@ -4092,7 +4092,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="111" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="111" spans="2:6">
       <c r="B111">
         <v>3</v>
       </c>
@@ -4109,7 +4109,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="112" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="112" spans="2:6">
       <c r="B112">
         <v>3</v>
       </c>
@@ -4126,7 +4126,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="114" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="114" spans="2:6">
       <c r="B114">
         <v>3</v>
       </c>
@@ -4143,7 +4143,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="115" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="115" spans="2:6">
       <c r="B115">
         <v>3</v>
       </c>
@@ -4160,7 +4160,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="116" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="116" spans="2:6">
       <c r="B116">
         <v>3</v>
       </c>
@@ -4177,7 +4177,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="118" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="118" spans="2:6">
       <c r="B118">
         <v>4</v>
       </c>
@@ -4188,7 +4188,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="119" spans="2:6" ht="17" x14ac:dyDescent="0.2">
+    <row r="119" spans="2:6">
       <c r="B119">
         <v>4</v>
       </c>
@@ -4199,7 +4199,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="120" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="120" spans="2:6">
       <c r="B120">
         <v>4</v>
       </c>
@@ -4210,7 +4210,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="121" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="121" spans="2:6">
       <c r="B121">
         <v>4</v>
       </c>
@@ -4221,7 +4221,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="122" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="122" spans="2:6">
       <c r="B122">
         <v>4</v>
       </c>
@@ -4232,7 +4232,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="123" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="123" spans="2:6">
       <c r="B123">
         <v>4</v>
       </c>
@@ -4243,7 +4243,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="125" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="125" spans="2:6">
       <c r="B125">
         <v>4</v>
       </c>
@@ -4254,7 +4254,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="126" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="126" spans="2:6">
       <c r="B126">
         <v>4</v>
       </c>
@@ -4265,7 +4265,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="127" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="127" spans="2:6">
       <c r="B127">
         <v>4</v>
       </c>
@@ -4276,7 +4276,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="128" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="128" spans="2:6">
       <c r="B128">
         <v>4</v>
       </c>
@@ -4287,7 +4287,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="129" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="129" spans="2:5">
       <c r="B129">
         <v>4</v>
       </c>
@@ -4298,7 +4298,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="130" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="130" spans="2:5">
       <c r="B130">
         <v>4</v>
       </c>
@@ -4309,7 +4309,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="131" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="131" spans="2:5">
       <c r="B131">
         <v>4</v>
       </c>
@@ -4320,7 +4320,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="132" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="132" spans="2:5">
       <c r="B132">
         <v>4</v>
       </c>
@@ -4331,7 +4331,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="133" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="133" spans="2:5">
       <c r="B133">
         <v>4</v>
       </c>
@@ -4342,7 +4342,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="134" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="134" spans="2:5">
       <c r="B134">
         <v>4</v>
       </c>
@@ -4353,7 +4353,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="135" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="135" spans="2:5">
       <c r="B135">
         <v>4</v>
       </c>
@@ -4364,7 +4364,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="137" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="137" spans="2:5">
       <c r="B137">
         <v>4</v>
       </c>
@@ -4375,7 +4375,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="138" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="138" spans="2:5">
       <c r="B138">
         <v>4</v>
       </c>
@@ -4386,7 +4386,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="139" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="139" spans="2:5">
       <c r="B139">
         <v>4</v>
       </c>
@@ -4397,7 +4397,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="140" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="140" spans="2:5">
       <c r="B140">
         <v>4</v>
       </c>
@@ -4408,7 +4408,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="142" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="142" spans="2:5">
       <c r="B142">
         <v>4</v>
       </c>
@@ -4419,7 +4419,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="143" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="143" spans="2:5">
       <c r="B143">
         <v>4</v>
       </c>
@@ -4430,7 +4430,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="144" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="144" spans="2:5">
       <c r="B144">
         <v>4</v>
       </c>
@@ -4441,7 +4441,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="145" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="145" spans="2:5">
       <c r="B145">
         <v>4</v>
       </c>
@@ -4452,7 +4452,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="146" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="146" spans="2:5">
       <c r="B146">
         <v>4</v>
       </c>
@@ -4463,7 +4463,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="147" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="147" spans="2:5">
       <c r="B147">
         <v>4</v>
       </c>
@@ -4474,7 +4474,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="148" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="148" spans="2:5">
       <c r="B148">
         <v>4</v>
       </c>
@@ -4485,7 +4485,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="150" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="150" spans="2:5">
       <c r="B150">
         <v>4</v>
       </c>
@@ -4496,7 +4496,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="151" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="151" spans="2:5">
       <c r="B151">
         <v>4</v>
       </c>
@@ -4507,7 +4507,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="152" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="152" spans="2:5">
       <c r="B152">
         <v>4</v>
       </c>
@@ -4518,7 +4518,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="153" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="153" spans="2:5">
       <c r="B153">
         <v>4</v>
       </c>
@@ -4529,7 +4529,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="154" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="154" spans="2:5">
       <c r="B154">
         <v>4</v>
       </c>
@@ -4540,7 +4540,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="155" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="155" spans="2:5">
       <c r="B155">
         <v>4</v>
       </c>
@@ -4551,7 +4551,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="156" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="156" spans="2:5">
       <c r="B156">
         <v>4</v>
       </c>
@@ -4562,7 +4562,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="157" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="157" spans="2:5">
       <c r="B157">
         <v>4</v>
       </c>
@@ -4573,7 +4573,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="158" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="158" spans="2:5">
       <c r="B158">
         <v>4</v>
       </c>
@@ -4584,7 +4584,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="159" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="159" spans="2:5">
       <c r="B159">
         <v>4</v>
       </c>
@@ -4595,7 +4595,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="161" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="161" spans="2:5">
       <c r="B161">
         <v>5</v>
       </c>
@@ -4606,7 +4606,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="162" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="162" spans="2:5">
       <c r="B162">
         <v>5</v>
       </c>
@@ -4617,7 +4617,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="163" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="163" spans="2:5">
       <c r="B163">
         <v>5</v>
       </c>
@@ -4628,7 +4628,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="164" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="164" spans="2:5">
       <c r="B164">
         <v>5</v>
       </c>
@@ -4639,7 +4639,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="165" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="165" spans="2:5">
       <c r="B165">
         <v>5</v>
       </c>
@@ -4650,7 +4650,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="166" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="166" spans="2:5">
       <c r="B166">
         <v>5</v>
       </c>
@@ -4661,7 +4661,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="167" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="167" spans="2:5">
       <c r="B167">
         <v>5</v>
       </c>
@@ -4672,7 +4672,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="169" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="169" spans="2:5">
       <c r="B169">
         <v>5</v>
       </c>
@@ -4683,7 +4683,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="170" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="170" spans="2:5">
       <c r="B170">
         <v>5</v>
       </c>
@@ -4694,7 +4694,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="171" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="171" spans="2:5">
       <c r="B171">
         <v>5</v>
       </c>
@@ -4705,7 +4705,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="172" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="172" spans="2:5">
       <c r="B172">
         <v>5</v>
       </c>
@@ -4716,7 +4716,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="173" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="173" spans="2:5">
       <c r="B173">
         <v>5</v>
       </c>
@@ -4727,7 +4727,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="175" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="175" spans="2:5">
       <c r="B175">
         <v>5</v>
       </c>
@@ -4738,7 +4738,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="176" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="176" spans="2:5">
       <c r="B176">
         <v>5</v>
       </c>
@@ -4749,7 +4749,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="177" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="177" spans="2:5">
       <c r="B177">
         <v>5</v>
       </c>
@@ -4760,7 +4760,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="178" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="178" spans="2:5">
       <c r="B178">
         <v>5</v>
       </c>
@@ -4771,7 +4771,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="179" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="179" spans="2:5">
       <c r="B179">
         <v>5</v>
       </c>
@@ -4782,7 +4782,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="180" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="180" spans="2:5">
       <c r="B180">
         <v>5</v>
       </c>
@@ -4793,7 +4793,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="181" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="181" spans="2:5">
       <c r="B181">
         <v>5</v>
       </c>
@@ -4804,7 +4804,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="182" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="182" spans="2:5">
       <c r="B182">
         <v>5</v>
       </c>
@@ -4815,7 +4815,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="184" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="184" spans="2:5">
       <c r="B184">
         <v>5</v>
       </c>
@@ -4826,7 +4826,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="185" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="185" spans="2:5">
       <c r="B185">
         <v>5</v>
       </c>
@@ -4837,7 +4837,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="186" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="186" spans="2:5">
       <c r="B186">
         <v>5</v>
       </c>
@@ -4848,7 +4848,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="187" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="187" spans="2:5">
       <c r="B187">
         <v>5</v>
       </c>
@@ -4859,7 +4859,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="188" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="188" spans="2:5">
       <c r="B188">
         <v>5</v>
       </c>
@@ -4870,7 +4870,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="189" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="189" spans="2:5">
       <c r="B189">
         <v>5</v>
       </c>
@@ -4881,7 +4881,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="190" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="190" spans="2:5">
       <c r="B190">
         <v>5</v>
       </c>
@@ -4892,7 +4892,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="191" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="191" spans="2:5">
       <c r="B191">
         <v>5</v>
       </c>
@@ -4903,7 +4903,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="193" spans="4:5" x14ac:dyDescent="0.2">
+    <row r="193" spans="4:5">
       <c r="D193" s="6"/>
       <c r="E193" s="7"/>
     </row>

--- a/Tasks.xlsx
+++ b/Tasks.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pas02\Nextcloud\Documents\03_Data Science - Uni Stuttgart\06_SoS 2026\04_Software Engineering\Group project 3\ai-travel-planner\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/exler/VSCode_Projects/ai-travel-planner/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6465E58-F374-294C-99D3-0E516C95C3C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDFE2DF2-5246-1A46-98DB-DE4000986756}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{834F46D4-8CFA-4605-9F2C-653FA769D6F4}"/>
+    <workbookView xWindow="0" yWindow="1240" windowWidth="34200" windowHeight="19660" xr2:uid="{834F46D4-8CFA-4605-9F2C-653FA769D6F4}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="466" uniqueCount="204">
   <si>
     <t>Project Setup</t>
   </si>
@@ -763,7 +763,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -891,7 +891,7 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="de-DE" b="1"/>
-              <a:t>Alpha Sprint Burn-down chart (day 2)</a:t>
+              <a:t>Alpha Sprint Burn-down chart (day 4)</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -1070,10 +1070,10 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Tabelle1!$L$5:$L$7</c:f>
+              <c:f>Tabelle1!$L$5:$L$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>165</c:v>
                 </c:pt>
@@ -1082,6 +1082,12 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>99</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>66</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>43</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2301,16 +2307,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67F1D602-D536-4BC9-865A-CD2C06CAE9C2}">
   <dimension ref="B2:M193"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="6.85546875" customWidth="1"/>
-    <col min="3" max="3" width="22.85546875" customWidth="1"/>
-    <col min="4" max="4" width="29.7109375" customWidth="1"/>
-    <col min="5" max="5" width="66.140625" customWidth="1"/>
-    <col min="6" max="6" width="12.42578125" customWidth="1"/>
+    <col min="2" max="2" width="6.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+    <col min="4" max="4" width="29.6640625" customWidth="1"/>
+    <col min="5" max="5" width="66.1640625" customWidth="1"/>
+    <col min="6" max="6" width="12.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:13" ht="21">
+    <row r="2" spans="2:13" ht="22" x14ac:dyDescent="0.3">
       <c r="B2" s="5" t="s">
         <v>191</v>
       </c>
@@ -2319,16 +2325,16 @@
         <v>192</v>
       </c>
     </row>
-    <row r="3" spans="2:13">
+    <row r="3" spans="2:13" x14ac:dyDescent="0.2">
       <c r="E3" s="4"/>
       <c r="K3" t="s">
         <v>199</v>
       </c>
       <c r="L3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="2:13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B4" s="1" t="s">
         <v>188</v>
       </c>
@@ -2360,7 +2366,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="5" spans="2:13">
+    <row r="5" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B5">
         <v>1</v>
       </c>
@@ -2393,7 +2399,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="6" spans="2:13">
+    <row r="6" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B6">
         <v>1</v>
       </c>
@@ -2429,7 +2435,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="7" spans="2:13">
+    <row r="7" spans="2:13" ht="17" x14ac:dyDescent="0.2">
       <c r="B7">
         <v>1</v>
       </c>
@@ -2469,7 +2475,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="8" spans="2:13">
+    <row r="8" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B8">
         <v>1</v>
       </c>
@@ -2500,16 +2506,16 @@
         <f t="shared" si="2"/>
         <v>66</v>
       </c>
-      <c r="L8" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M8" t="str">
+      <c r="L8">
+        <f>IF(H8&gt;$L$3,"",L7-J8)</f>
+        <v>66</v>
+      </c>
+      <c r="M8">
         <f>IF(H8&gt;$L$3,"",L8)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" spans="2:13">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="9" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B9">
         <v>1</v>
       </c>
@@ -2534,22 +2540,22 @@
       </c>
       <c r="J9">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="K9">
         <f t="shared" si="2"/>
         <v>28</v>
       </c>
-      <c r="L9" t="str">
+      <c r="L9">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M9" t="str">
+        <v>43</v>
+      </c>
+      <c r="M9">
         <f>IF(H9&gt;$L$3,"",L9)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" spans="2:13">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B10">
         <v>1</v>
       </c>
@@ -2589,7 +2595,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="2:13">
+    <row r="11" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B11">
         <v>1</v>
       </c>
@@ -2613,7 +2619,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="12" spans="2:13">
+    <row r="12" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B12">
         <v>1</v>
       </c>
@@ -2630,7 +2636,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="2:13">
+    <row r="14" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B14">
         <v>1</v>
       </c>
@@ -2647,7 +2653,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="2:13">
+    <row r="15" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B15">
         <v>1</v>
       </c>
@@ -2664,7 +2670,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="2:13">
+    <row r="16" spans="2:13" ht="17" x14ac:dyDescent="0.2">
       <c r="B16">
         <v>1</v>
       </c>
@@ -2681,7 +2687,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="2:6">
+    <row r="17" spans="2:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B17">
         <v>1</v>
       </c>
@@ -2698,7 +2704,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="2:6">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B18">
         <v>1</v>
       </c>
@@ -2715,7 +2721,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="2:6">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B19">
         <v>1</v>
       </c>
@@ -2732,7 +2738,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="2:6">
+    <row r="20" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B20">
         <v>1</v>
       </c>
@@ -2749,7 +2755,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="2:6">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22">
         <v>1</v>
       </c>
@@ -2766,7 +2772,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="2:6">
+    <row r="23" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B23">
         <v>1</v>
       </c>
@@ -2783,7 +2789,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="2:6">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B24">
         <v>1</v>
       </c>
@@ -2800,7 +2806,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="2:6">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B25">
         <v>1</v>
       </c>
@@ -2817,7 +2823,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="2:6">
+    <row r="26" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B26">
         <v>1</v>
       </c>
@@ -2834,7 +2840,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="2:6">
+    <row r="27" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B27">
         <v>1</v>
       </c>
@@ -2851,7 +2857,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="2:6">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B28">
         <v>1</v>
       </c>
@@ -2868,7 +2874,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="2:6">
+    <row r="29" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B29">
         <v>1</v>
       </c>
@@ -2885,7 +2891,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="2:6">
+    <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30">
         <v>1</v>
       </c>
@@ -2902,7 +2908,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="2:6">
+    <row r="31" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B31">
         <v>1</v>
       </c>
@@ -2919,7 +2925,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="2:6">
+    <row r="32" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B32">
         <v>1</v>
       </c>
@@ -2936,7 +2942,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="2:6">
+    <row r="33" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B33">
         <v>1</v>
       </c>
@@ -2953,7 +2959,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="2:6">
+    <row r="34" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B34">
         <v>1</v>
       </c>
@@ -2970,7 +2976,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="2:6">
+    <row r="36" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B36">
         <v>1</v>
       </c>
@@ -2987,7 +2993,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="2:6">
+    <row r="37" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B37">
         <v>1</v>
       </c>
@@ -3004,7 +3010,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="2:6">
+    <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38">
         <v>1</v>
       </c>
@@ -3021,7 +3027,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="2:6">
+    <row r="39" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B39">
         <v>1</v>
       </c>
@@ -3038,7 +3044,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="2:6">
+    <row r="40" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B40">
         <v>1</v>
       </c>
@@ -3055,7 +3061,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="2:6">
+    <row r="42" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B42">
         <v>2</v>
       </c>
@@ -3072,7 +3078,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="43" spans="2:6">
+    <row r="43" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B43">
         <v>2</v>
       </c>
@@ -3089,7 +3095,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="44" spans="2:6">
+    <row r="44" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B44">
         <v>2</v>
       </c>
@@ -3106,7 +3112,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="45" spans="2:6">
+    <row r="45" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B45">
         <v>2</v>
       </c>
@@ -3123,7 +3129,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="46" spans="2:6">
+    <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46">
         <v>2</v>
       </c>
@@ -3140,7 +3146,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="47" spans="2:6">
+    <row r="47" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B47">
         <v>2</v>
       </c>
@@ -3157,7 +3163,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="48" spans="2:6">
+    <row r="48" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B48">
         <v>2</v>
       </c>
@@ -3174,7 +3180,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="2:6">
+    <row r="50" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B50">
         <v>2</v>
       </c>
@@ -3191,7 +3197,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="51" spans="2:6">
+    <row r="51" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B51">
         <v>2</v>
       </c>
@@ -3208,7 +3214,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="52" spans="2:6">
+    <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52">
         <v>2</v>
       </c>
@@ -3225,7 +3231,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="53" spans="2:6">
+    <row r="53" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B53">
         <v>2</v>
       </c>
@@ -3242,7 +3248,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="2:6">
+    <row r="54" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B54">
         <v>2</v>
       </c>
@@ -3259,7 +3265,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="55" spans="2:6">
+    <row r="55" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B55">
         <v>2</v>
       </c>
@@ -3276,7 +3282,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="57" spans="2:6">
+    <row r="57" spans="2:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B57">
         <v>2</v>
       </c>
@@ -3293,7 +3299,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="58" spans="2:6">
+    <row r="58" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B58">
         <v>2</v>
       </c>
@@ -3310,7 +3316,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="59" spans="2:6">
+    <row r="59" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B59">
         <v>2</v>
       </c>
@@ -3327,7 +3333,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="60" spans="2:6">
+    <row r="60" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B60">
         <v>2</v>
       </c>
@@ -3344,7 +3350,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="61" spans="2:6">
+    <row r="61" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B61">
         <v>2</v>
       </c>
@@ -3361,7 +3367,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="62" spans="2:6">
+    <row r="62" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B62">
         <v>2</v>
       </c>
@@ -3378,7 +3384,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="64" spans="2:6">
+    <row r="64" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B64">
         <v>2</v>
       </c>
@@ -3395,7 +3401,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="65" spans="2:6">
+    <row r="65" spans="2:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B65">
         <v>2</v>
       </c>
@@ -3412,7 +3418,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="66" spans="2:6">
+    <row r="66" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B66">
         <v>2</v>
       </c>
@@ -3429,7 +3435,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="67" spans="2:6">
+    <row r="67" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B67">
         <v>2</v>
       </c>
@@ -3446,7 +3452,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="68" spans="2:6">
+    <row r="68" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B68">
         <v>2</v>
       </c>
@@ -3463,7 +3469,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="69" spans="2:6">
+    <row r="69" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B69">
         <v>2</v>
       </c>
@@ -3480,7 +3486,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="71" spans="2:6">
+    <row r="71" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B71">
         <v>2</v>
       </c>
@@ -3497,7 +3503,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="72" spans="2:6">
+    <row r="72" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B72">
         <v>2</v>
       </c>
@@ -3514,7 +3520,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="73" spans="2:6">
+    <row r="73" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B73">
         <v>2</v>
       </c>
@@ -3531,7 +3537,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="74" spans="2:6">
+    <row r="74" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B74">
         <v>2</v>
       </c>
@@ -3548,7 +3554,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="75" spans="2:6">
+    <row r="75" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B75">
         <v>2</v>
       </c>
@@ -3565,7 +3571,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="76" spans="2:6">
+    <row r="76" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B76">
         <v>2</v>
       </c>
@@ -3582,7 +3588,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="77" spans="2:6">
+    <row r="77" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B77">
         <v>2</v>
       </c>
@@ -3599,7 +3605,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="78" spans="2:6">
+    <row r="78" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B78">
         <v>2</v>
       </c>
@@ -3616,7 +3622,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="80" spans="2:6">
+    <row r="80" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B80">
         <v>3</v>
       </c>
@@ -3633,7 +3639,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="81" spans="2:6">
+    <row r="81" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B81">
         <v>3</v>
       </c>
@@ -3650,7 +3656,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="82" spans="2:6">
+    <row r="82" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B82">
         <v>3</v>
       </c>
@@ -3667,7 +3673,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="83" spans="2:6">
+    <row r="83" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B83">
         <v>3</v>
       </c>
@@ -3684,7 +3690,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="85" spans="2:6">
+    <row r="85" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B85">
         <v>3</v>
       </c>
@@ -3701,7 +3707,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="86" spans="2:6">
+    <row r="86" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B86">
         <v>3</v>
       </c>
@@ -3718,7 +3724,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="87" spans="2:6">
+    <row r="87" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B87">
         <v>3</v>
       </c>
@@ -3735,7 +3741,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="88" spans="2:6">
+    <row r="88" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B88">
         <v>3</v>
       </c>
@@ -3752,7 +3758,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="89" spans="2:6">
+    <row r="89" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B89">
         <v>3</v>
       </c>
@@ -3769,7 +3775,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="90" spans="2:6">
+    <row r="90" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B90">
         <v>3</v>
       </c>
@@ -3786,7 +3792,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="91" spans="2:6">
+    <row r="91" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B91">
         <v>3</v>
       </c>
@@ -3803,7 +3809,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="92" spans="2:6">
+    <row r="92" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B92">
         <v>3</v>
       </c>
@@ -3820,7 +3826,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="93" spans="2:6">
+    <row r="93" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B93">
         <v>3</v>
       </c>
@@ -3837,7 +3843,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="94" spans="2:6">
+    <row r="94" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B94">
         <v>3</v>
       </c>
@@ -3854,7 +3860,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="95" spans="2:6">
+    <row r="95" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B95">
         <v>3</v>
       </c>
@@ -3871,7 +3877,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="97" spans="2:6">
+    <row r="97" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B97">
         <v>3</v>
       </c>
@@ -3888,7 +3894,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="98" spans="2:6">
+    <row r="98" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B98">
         <v>3</v>
       </c>
@@ -3905,7 +3911,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="99" spans="2:6">
+    <row r="99" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B99">
         <v>3</v>
       </c>
@@ -3922,7 +3928,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="100" spans="2:6">
+    <row r="100" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B100">
         <v>3</v>
       </c>
@@ -3939,7 +3945,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="101" spans="2:6">
+    <row r="101" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B101">
         <v>3</v>
       </c>
@@ -3956,7 +3962,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="102" spans="2:6">
+    <row r="102" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B102">
         <v>3</v>
       </c>
@@ -3973,7 +3979,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="103" spans="2:6">
+    <row r="103" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B103">
         <v>3</v>
       </c>
@@ -3990,7 +3996,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="104" spans="2:6">
+    <row r="104" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B104">
         <v>3</v>
       </c>
@@ -4007,7 +4013,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="105" spans="2:6">
+    <row r="105" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B105">
         <v>3</v>
       </c>
@@ -4024,7 +4030,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="106" spans="2:6">
+    <row r="106" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B106">
         <v>3</v>
       </c>
@@ -4041,7 +4047,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="108" spans="2:6">
+    <row r="108" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B108">
         <v>3</v>
       </c>
@@ -4058,7 +4064,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="109" spans="2:6">
+    <row r="109" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B109">
         <v>3</v>
       </c>
@@ -4075,7 +4081,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="110" spans="2:6">
+    <row r="110" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B110">
         <v>3</v>
       </c>
@@ -4092,7 +4098,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="111" spans="2:6">
+    <row r="111" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B111">
         <v>3</v>
       </c>
@@ -4109,7 +4115,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="112" spans="2:6">
+    <row r="112" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B112">
         <v>3</v>
       </c>
@@ -4126,7 +4132,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="114" spans="2:6">
+    <row r="114" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B114">
         <v>3</v>
       </c>
@@ -4143,7 +4149,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="115" spans="2:6">
+    <row r="115" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B115">
         <v>3</v>
       </c>
@@ -4160,7 +4166,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="116" spans="2:6">
+    <row r="116" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B116">
         <v>3</v>
       </c>
@@ -4177,7 +4183,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="118" spans="2:6">
+    <row r="118" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B118">
         <v>4</v>
       </c>
@@ -4188,7 +4194,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="119" spans="2:6">
+    <row r="119" spans="2:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B119">
         <v>4</v>
       </c>
@@ -4199,7 +4205,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="120" spans="2:6">
+    <row r="120" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B120">
         <v>4</v>
       </c>
@@ -4210,7 +4216,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="121" spans="2:6">
+    <row r="121" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B121">
         <v>4</v>
       </c>
@@ -4221,7 +4227,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="122" spans="2:6">
+    <row r="122" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B122">
         <v>4</v>
       </c>
@@ -4232,7 +4238,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="123" spans="2:6">
+    <row r="123" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B123">
         <v>4</v>
       </c>
@@ -4243,9 +4249,12 @@
         <v>113</v>
       </c>
     </row>
-    <row r="125" spans="2:6">
+    <row r="125" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B125">
         <v>4</v>
+      </c>
+      <c r="C125" t="s">
+        <v>201</v>
       </c>
       <c r="D125" s="3" t="s">
         <v>114</v>
@@ -4253,10 +4262,16 @@
       <c r="E125" s="2" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="126" spans="2:6">
+      <c r="F125">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="126" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B126">
         <v>4</v>
+      </c>
+      <c r="C126" t="s">
+        <v>201</v>
       </c>
       <c r="D126" s="3" t="s">
         <v>114</v>
@@ -4264,10 +4279,16 @@
       <c r="E126" s="2" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="127" spans="2:6">
+      <c r="F126">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="127" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B127">
         <v>4</v>
+      </c>
+      <c r="C127" t="s">
+        <v>201</v>
       </c>
       <c r="D127" s="3" t="s">
         <v>114</v>
@@ -4275,10 +4296,16 @@
       <c r="E127" s="2" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="128" spans="2:6">
+      <c r="F127">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="128" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B128">
         <v>4</v>
+      </c>
+      <c r="C128" t="s">
+        <v>201</v>
       </c>
       <c r="D128" s="3" t="s">
         <v>114</v>
@@ -4286,10 +4313,16 @@
       <c r="E128" s="2" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="129" spans="2:5">
+      <c r="F128">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="129" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B129">
         <v>4</v>
+      </c>
+      <c r="C129" t="s">
+        <v>201</v>
       </c>
       <c r="D129" s="3" t="s">
         <v>114</v>
@@ -4297,10 +4330,16 @@
       <c r="E129" s="2" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="130" spans="2:5">
+      <c r="F129">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="130" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B130">
         <v>4</v>
+      </c>
+      <c r="C130" t="s">
+        <v>201</v>
       </c>
       <c r="D130" s="3" t="s">
         <v>114</v>
@@ -4308,10 +4347,16 @@
       <c r="E130" s="2" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="131" spans="2:5">
+      <c r="F130">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="131" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B131">
         <v>4</v>
+      </c>
+      <c r="C131" t="s">
+        <v>201</v>
       </c>
       <c r="D131" s="3" t="s">
         <v>114</v>
@@ -4319,10 +4364,16 @@
       <c r="E131" s="2" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="132" spans="2:5">
+      <c r="F131">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="132" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B132">
         <v>4</v>
+      </c>
+      <c r="C132" t="s">
+        <v>201</v>
       </c>
       <c r="D132" s="3" t="s">
         <v>114</v>
@@ -4330,10 +4381,16 @@
       <c r="E132" s="2" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="133" spans="2:5">
+      <c r="F132">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="133" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B133">
         <v>4</v>
+      </c>
+      <c r="C133" t="s">
+        <v>201</v>
       </c>
       <c r="D133" s="3" t="s">
         <v>114</v>
@@ -4341,10 +4398,16 @@
       <c r="E133" s="2" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="134" spans="2:5">
+      <c r="F133">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="134" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B134">
         <v>4</v>
+      </c>
+      <c r="C134" t="s">
+        <v>201</v>
       </c>
       <c r="D134" s="3" t="s">
         <v>114</v>
@@ -4352,10 +4415,16 @@
       <c r="E134" s="2" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="135" spans="2:5">
+      <c r="F134">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="135" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B135">
         <v>4</v>
+      </c>
+      <c r="C135" t="s">
+        <v>201</v>
       </c>
       <c r="D135" s="3" t="s">
         <v>114</v>
@@ -4363,8 +4432,11 @@
       <c r="E135" s="2" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="137" spans="2:5">
+      <c r="F135">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="137" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B137">
         <v>4</v>
       </c>
@@ -4375,7 +4447,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="138" spans="2:5">
+    <row r="138" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B138">
         <v>4</v>
       </c>
@@ -4386,7 +4458,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="139" spans="2:5">
+    <row r="139" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B139">
         <v>4</v>
       </c>
@@ -4397,7 +4469,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="140" spans="2:5">
+    <row r="140" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B140">
         <v>4</v>
       </c>
@@ -4408,9 +4480,12 @@
         <v>130</v>
       </c>
     </row>
-    <row r="142" spans="2:5">
+    <row r="142" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B142">
         <v>4</v>
+      </c>
+      <c r="C142" t="s">
+        <v>202</v>
       </c>
       <c r="D142" s="3" t="s">
         <v>131</v>
@@ -4418,10 +4493,16 @@
       <c r="E142" s="2" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="143" spans="2:5">
+      <c r="F142">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="143" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B143">
         <v>4</v>
+      </c>
+      <c r="C143" t="s">
+        <v>202</v>
       </c>
       <c r="D143" s="3" t="s">
         <v>131</v>
@@ -4429,10 +4510,16 @@
       <c r="E143" s="2" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="144" spans="2:5">
+      <c r="F143">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="144" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B144">
         <v>4</v>
+      </c>
+      <c r="C144" t="s">
+        <v>202</v>
       </c>
       <c r="D144" s="3" t="s">
         <v>131</v>
@@ -4440,10 +4527,16 @@
       <c r="E144" s="2" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="145" spans="2:5">
+      <c r="F144">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="145" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B145">
         <v>4</v>
+      </c>
+      <c r="C145" t="s">
+        <v>202</v>
       </c>
       <c r="D145" s="3" t="s">
         <v>131</v>
@@ -4451,10 +4544,16 @@
       <c r="E145" s="2" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="146" spans="2:5">
+      <c r="F145">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="146" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B146">
         <v>4</v>
+      </c>
+      <c r="C146" t="s">
+        <v>202</v>
       </c>
       <c r="D146" s="3" t="s">
         <v>131</v>
@@ -4462,10 +4561,16 @@
       <c r="E146" s="2" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="147" spans="2:5">
+      <c r="F146">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="147" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B147">
         <v>4</v>
+      </c>
+      <c r="C147" t="s">
+        <v>203</v>
       </c>
       <c r="D147" s="3" t="s">
         <v>131</v>
@@ -4473,10 +4578,16 @@
       <c r="E147" s="2" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="148" spans="2:5">
+      <c r="F147">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="148" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B148">
         <v>4</v>
+      </c>
+      <c r="C148" t="s">
+        <v>203</v>
       </c>
       <c r="D148" s="3" t="s">
         <v>131</v>
@@ -4484,10 +4595,16 @@
       <c r="E148" s="2" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="150" spans="2:5">
+      <c r="F148">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="150" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B150">
         <v>4</v>
+      </c>
+      <c r="C150" t="s">
+        <v>203</v>
       </c>
       <c r="D150" s="3" t="s">
         <v>139</v>
@@ -4495,8 +4612,11 @@
       <c r="E150" s="2" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="151" spans="2:5">
+      <c r="F150">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="151" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B151">
         <v>4</v>
       </c>
@@ -4507,9 +4627,12 @@
         <v>141</v>
       </c>
     </row>
-    <row r="152" spans="2:5">
+    <row r="152" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B152">
         <v>4</v>
+      </c>
+      <c r="C152" t="s">
+        <v>203</v>
       </c>
       <c r="D152" s="3" t="s">
         <v>139</v>
@@ -4517,8 +4640,11 @@
       <c r="E152" s="2" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="153" spans="2:5">
+      <c r="F152">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="153" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B153">
         <v>4</v>
       </c>
@@ -4529,7 +4655,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="154" spans="2:5">
+    <row r="154" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B154">
         <v>4</v>
       </c>
@@ -4540,7 +4666,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="155" spans="2:5">
+    <row r="155" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B155">
         <v>4</v>
       </c>
@@ -4551,9 +4677,12 @@
         <v>145</v>
       </c>
     </row>
-    <row r="156" spans="2:5">
+    <row r="156" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B156">
         <v>4</v>
+      </c>
+      <c r="C156" t="s">
+        <v>203</v>
       </c>
       <c r="D156" s="3" t="s">
         <v>139</v>
@@ -4561,10 +4690,16 @@
       <c r="E156" s="2" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="157" spans="2:5">
+      <c r="F156">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="157" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B157">
         <v>4</v>
+      </c>
+      <c r="C157" t="s">
+        <v>203</v>
       </c>
       <c r="D157" s="3" t="s">
         <v>139</v>
@@ -4572,10 +4707,16 @@
       <c r="E157" s="2" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="158" spans="2:5">
+      <c r="F157">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="158" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B158">
         <v>4</v>
+      </c>
+      <c r="C158" t="s">
+        <v>203</v>
       </c>
       <c r="D158" s="3" t="s">
         <v>139</v>
@@ -4583,8 +4724,11 @@
       <c r="E158" s="2" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="159" spans="2:5">
+      <c r="F158">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="159" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B159">
         <v>4</v>
       </c>
@@ -4595,7 +4739,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="161" spans="2:5">
+    <row r="161" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B161">
         <v>5</v>
       </c>
@@ -4606,7 +4750,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="162" spans="2:5">
+    <row r="162" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B162">
         <v>5</v>
       </c>
@@ -4617,7 +4761,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="163" spans="2:5">
+    <row r="163" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B163">
         <v>5</v>
       </c>
@@ -4628,7 +4772,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="164" spans="2:5">
+    <row r="164" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B164">
         <v>5</v>
       </c>
@@ -4639,7 +4783,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="165" spans="2:5">
+    <row r="165" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B165">
         <v>5</v>
       </c>
@@ -4650,7 +4794,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="166" spans="2:5">
+    <row r="166" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B166">
         <v>5</v>
       </c>
@@ -4661,7 +4805,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="167" spans="2:5">
+    <row r="167" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B167">
         <v>5</v>
       </c>
@@ -4672,7 +4816,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="169" spans="2:5">
+    <row r="169" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B169">
         <v>5</v>
       </c>
@@ -4683,7 +4827,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="170" spans="2:5">
+    <row r="170" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B170">
         <v>5</v>
       </c>
@@ -4694,7 +4838,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="171" spans="2:5">
+    <row r="171" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B171">
         <v>5</v>
       </c>
@@ -4705,7 +4849,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="172" spans="2:5">
+    <row r="172" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B172">
         <v>5</v>
       </c>
@@ -4716,7 +4860,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="173" spans="2:5">
+    <row r="173" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B173">
         <v>5</v>
       </c>
@@ -4727,7 +4871,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="175" spans="2:5">
+    <row r="175" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B175">
         <v>5</v>
       </c>
@@ -4738,7 +4882,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="176" spans="2:5">
+    <row r="176" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B176">
         <v>5</v>
       </c>
@@ -4749,7 +4893,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="177" spans="2:5">
+    <row r="177" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B177">
         <v>5</v>
       </c>
@@ -4760,7 +4904,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="178" spans="2:5">
+    <row r="178" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B178">
         <v>5</v>
       </c>
@@ -4771,7 +4915,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="179" spans="2:5">
+    <row r="179" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B179">
         <v>5</v>
       </c>
@@ -4782,7 +4926,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="180" spans="2:5">
+    <row r="180" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B180">
         <v>5</v>
       </c>
@@ -4793,7 +4937,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="181" spans="2:5">
+    <row r="181" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B181">
         <v>5</v>
       </c>
@@ -4804,7 +4948,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="182" spans="2:5">
+    <row r="182" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B182">
         <v>5</v>
       </c>
@@ -4815,7 +4959,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="184" spans="2:5">
+    <row r="184" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B184">
         <v>5</v>
       </c>
@@ -4826,7 +4970,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="185" spans="2:5">
+    <row r="185" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B185">
         <v>5</v>
       </c>
@@ -4837,7 +4981,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="186" spans="2:5">
+    <row r="186" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B186">
         <v>5</v>
       </c>
@@ -4848,7 +4992,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="187" spans="2:5">
+    <row r="187" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B187">
         <v>5</v>
       </c>
@@ -4859,7 +5003,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="188" spans="2:5">
+    <row r="188" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B188">
         <v>5</v>
       </c>
@@ -4870,7 +5014,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="189" spans="2:5">
+    <row r="189" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B189">
         <v>5</v>
       </c>
@@ -4881,7 +5025,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="190" spans="2:5">
+    <row r="190" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B190">
         <v>5</v>
       </c>
@@ -4892,7 +5036,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="191" spans="2:5">
+    <row r="191" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B191">
         <v>5</v>
       </c>
@@ -4903,7 +5047,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="193" spans="4:5">
+    <row r="193" spans="4:5" x14ac:dyDescent="0.2">
       <c r="D193" s="6"/>
       <c r="E193" s="7"/>
     </row>

--- a/Tasks.xlsx
+++ b/Tasks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/exler/VSCode_Projects/ai-travel-planner/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDFE2DF2-5246-1A46-98DB-DE4000986756}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40CBEFF7-254B-CB45-AFB2-C142EC3856A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1240" windowWidth="34200" windowHeight="19660" xr2:uid="{834F46D4-8CFA-4605-9F2C-653FA769D6F4}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="21460" xr2:uid="{834F46D4-8CFA-4605-9F2C-653FA769D6F4}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -891,7 +891,7 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="de-DE" b="1"/>
-              <a:t>Alpha Sprint Burn-down chart (day 4)</a:t>
+              <a:t>Alpha Sprint Burn-down chart (day 5)</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -1070,10 +1070,10 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Tabelle1!$L$5:$L$9</c:f>
+              <c:f>Tabelle1!$L$5:$L$10</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>165</c:v>
                 </c:pt>
@@ -1088,6 +1088,9 @@
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>43</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>26</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2331,7 +2334,7 @@
         <v>199</v>
       </c>
       <c r="L3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.2">
@@ -2580,19 +2583,19 @@
       </c>
       <c r="J10">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="K10">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L10" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M10" t="str">
+      <c r="L10">
+        <f>IF(H10&gt;$L$3,"",L9-J10)</f>
+        <v>26</v>
+      </c>
+      <c r="M10">
         <f>IF(H10&gt;$L$3,"",L10)</f>
-        <v/>
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="2:13" x14ac:dyDescent="0.2">
@@ -4193,6 +4196,9 @@
       <c r="E118" s="2" t="s">
         <v>109</v>
       </c>
+      <c r="F118">
+        <v>5</v>
+      </c>
     </row>
     <row r="119" spans="2:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B119">
@@ -4204,6 +4210,9 @@
       <c r="E119" s="2" t="s">
         <v>187</v>
       </c>
+      <c r="F119">
+        <v>5</v>
+      </c>
     </row>
     <row r="120" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B120">
@@ -4215,6 +4224,9 @@
       <c r="E120" s="2" t="s">
         <v>110</v>
       </c>
+      <c r="F120">
+        <v>5</v>
+      </c>
     </row>
     <row r="121" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B121">
@@ -4226,6 +4238,9 @@
       <c r="E121" s="2" t="s">
         <v>111</v>
       </c>
+      <c r="F121">
+        <v>5</v>
+      </c>
     </row>
     <row r="122" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B122">
@@ -4237,6 +4252,9 @@
       <c r="E122" s="2" t="s">
         <v>112</v>
       </c>
+      <c r="F122">
+        <v>5</v>
+      </c>
     </row>
     <row r="123" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B123">
@@ -4248,6 +4266,9 @@
       <c r="E123" s="2" t="s">
         <v>113</v>
       </c>
+      <c r="F123">
+        <v>5</v>
+      </c>
     </row>
     <row r="125" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B125">
@@ -4446,6 +4467,9 @@
       <c r="E137" s="2" t="s">
         <v>127</v>
       </c>
+      <c r="F137">
+        <v>5</v>
+      </c>
     </row>
     <row r="138" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B138">
@@ -4457,6 +4481,9 @@
       <c r="E138" s="2" t="s">
         <v>128</v>
       </c>
+      <c r="F138">
+        <v>5</v>
+      </c>
     </row>
     <row r="139" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B139">
@@ -4468,6 +4495,9 @@
       <c r="E139" s="2" t="s">
         <v>129</v>
       </c>
+      <c r="F139">
+        <v>5</v>
+      </c>
     </row>
     <row r="140" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B140">
@@ -4479,6 +4509,9 @@
       <c r="E140" s="2" t="s">
         <v>130</v>
       </c>
+      <c r="F140">
+        <v>5</v>
+      </c>
     </row>
     <row r="142" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B142">
@@ -4739,7 +4772,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="161" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="161" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B161">
         <v>5</v>
       </c>
@@ -4749,8 +4782,11 @@
       <c r="E161" s="2" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="162" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="F161">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="162" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B162">
         <v>5</v>
       </c>
@@ -4760,8 +4796,11 @@
       <c r="E162" s="2" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="163" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="F162">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="163" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B163">
         <v>5</v>
       </c>
@@ -4771,8 +4810,11 @@
       <c r="E163" s="2" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="164" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="F163">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="164" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B164">
         <v>5</v>
       </c>
@@ -4782,8 +4824,11 @@
       <c r="E164" s="2" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="165" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="F164">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="165" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B165">
         <v>5</v>
       </c>
@@ -4793,8 +4838,11 @@
       <c r="E165" s="2" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="166" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="F165">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="166" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B166">
         <v>5</v>
       </c>
@@ -4804,8 +4852,11 @@
       <c r="E166" s="2" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="167" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="F166">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="167" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B167">
         <v>5</v>
       </c>
@@ -4815,8 +4866,11 @@
       <c r="E167" s="2" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="169" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="F167">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="169" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B169">
         <v>5</v>
       </c>
@@ -4827,7 +4881,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="170" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="170" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B170">
         <v>5</v>
       </c>
@@ -4838,7 +4892,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="171" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="171" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B171">
         <v>5</v>
       </c>
@@ -4849,7 +4903,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="172" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="172" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B172">
         <v>5</v>
       </c>
@@ -4860,7 +4914,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="173" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="173" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B173">
         <v>5</v>
       </c>
@@ -4871,7 +4925,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="175" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="175" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B175">
         <v>5</v>
       </c>
@@ -4882,7 +4936,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="176" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="176" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B176">
         <v>5</v>
       </c>
